--- a/nablarch_sample/アプリケーション方式設計書_6出力処理方式_6.2.ファイル転送（配信）.xlsx
+++ b/nablarch_sample/アプリケーション方式設計書_6出力処理方式_6.2.ファイル転送（配信）.xlsx
@@ -1,23 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4975FB5-C7CC-4A21-990D-E4F2617288AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26130"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34E61990-0929-4AEA-996B-DAF19F6C4354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="6.2.ファイル転送（配信）" sheetId="4" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'6.2.ファイル転送（配信）'!$A$1:$AI$164</definedName>
-    <definedName name="Z_344DE406_F393_4E5A_9A14_596BA958D606_.wvu.PrintArea" localSheetId="0" hidden="1">'6.2.ファイル転送（配信）'!$A$1:$AI$164</definedName>
-    <definedName name="Z_8C881184_F554_455B_85E9_7E00CAD758E3_.wvu.PrintArea" localSheetId="0" hidden="1">'6.2.ファイル転送（配信）'!$A$1:$AI$164</definedName>
-    <definedName name="Z_AC3D26AC_6835_49DE_BCEC_94F40C257790_.wvu.PrintArea" localSheetId="0" hidden="1">'6.2.ファイル転送（配信）'!$A$1:$AI$164</definedName>
-    <definedName name="Z_B9596DFB_62BC_4685_B6E9_D37718868A8E_.wvu.PrintArea" localSheetId="0" hidden="1">'6.2.ファイル転送（配信）'!$A$1:$AI$164</definedName>
-    <definedName name="Z_E93A55B4_B092_4477_988B_A2DD8C792DE3_.wvu.PrintArea" localSheetId="0" hidden="1">'6.2.ファイル転送（配信）'!$A$1:$AI$164</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -1089,72 +1081,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1181,6 +1107,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="1" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="2" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="3" xfId="3" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -1214,6 +1149,63 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -5610,148 +5602,148 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AI595"/>
-  <sheetFormatPr defaultColWidth="3.6328125" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="3.625" defaultRowHeight="14.25" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="3.6328125" style="4"/>
+    <col min="1" max="16384" width="3.625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="3"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="53"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="75"/>
+      <c r="G1" s="75"/>
+      <c r="H1" s="75"/>
+      <c r="I1" s="75"/>
+      <c r="J1" s="75"/>
+      <c r="K1" s="75"/>
+      <c r="L1" s="75"/>
+      <c r="M1" s="75"/>
+      <c r="N1" s="75"/>
+      <c r="O1" s="76"/>
       <c r="P1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="Q1" s="2"/>
-      <c r="R1" s="54" t="s">
+      <c r="R1" s="77" t="s">
         <v>56</v>
       </c>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="55"/>
-      <c r="V1" s="55"/>
-      <c r="W1" s="55"/>
-      <c r="X1" s="56"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="78"/>
+      <c r="W1" s="78"/>
+      <c r="X1" s="79"/>
       <c r="Y1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="Z1" s="3"/>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="58"/>
-      <c r="AC1" s="58"/>
-      <c r="AD1" s="58"/>
-      <c r="AE1" s="59"/>
+      <c r="AA1" s="80"/>
+      <c r="AB1" s="81"/>
+      <c r="AC1" s="81"/>
+      <c r="AD1" s="81"/>
+      <c r="AE1" s="82"/>
       <c r="AF1" s="60"/>
       <c r="AG1" s="61"/>
       <c r="AH1" s="61"/>
       <c r="AI1" s="62"/>
     </row>
-    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="7"/>
-      <c r="E2" s="63"/>
-      <c r="F2" s="64"/>
-      <c r="G2" s="64"/>
-      <c r="H2" s="64"/>
-      <c r="I2" s="64"/>
-      <c r="J2" s="64"/>
-      <c r="K2" s="64"/>
-      <c r="L2" s="64"/>
-      <c r="M2" s="64"/>
-      <c r="N2" s="64"/>
-      <c r="O2" s="65"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="84"/>
+      <c r="G2" s="84"/>
+      <c r="H2" s="84"/>
+      <c r="I2" s="84"/>
+      <c r="J2" s="84"/>
+      <c r="K2" s="84"/>
+      <c r="L2" s="84"/>
+      <c r="M2" s="84"/>
+      <c r="N2" s="84"/>
+      <c r="O2" s="85"/>
       <c r="P2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="Q2" s="9"/>
-      <c r="R2" s="66" t="s">
+      <c r="R2" s="86" t="s">
         <v>5</v>
       </c>
-      <c r="S2" s="67"/>
-      <c r="T2" s="67"/>
-      <c r="U2" s="67"/>
-      <c r="V2" s="67"/>
-      <c r="W2" s="67"/>
-      <c r="X2" s="68"/>
+      <c r="S2" s="87"/>
+      <c r="T2" s="87"/>
+      <c r="U2" s="87"/>
+      <c r="V2" s="87"/>
+      <c r="W2" s="87"/>
+      <c r="X2" s="88"/>
       <c r="Y2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="Z2" s="3"/>
-      <c r="AA2" s="57"/>
-      <c r="AB2" s="58"/>
-      <c r="AC2" s="58"/>
-      <c r="AD2" s="58"/>
-      <c r="AE2" s="59"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="81"/>
+      <c r="AC2" s="81"/>
+      <c r="AD2" s="81"/>
+      <c r="AE2" s="82"/>
       <c r="AF2" s="60"/>
       <c r="AG2" s="61"/>
       <c r="AH2" s="61"/>
       <c r="AI2" s="62"/>
     </row>
-    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="11"/>
       <c r="D3" s="3"/>
-      <c r="E3" s="72"/>
-      <c r="F3" s="72"/>
-      <c r="G3" s="72"/>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
-      <c r="J3" s="72"/>
-      <c r="K3" s="72"/>
-      <c r="L3" s="72"/>
-      <c r="M3" s="72"/>
-      <c r="N3" s="72"/>
-      <c r="O3" s="72"/>
+      <c r="E3" s="92"/>
+      <c r="F3" s="92"/>
+      <c r="G3" s="92"/>
+      <c r="H3" s="92"/>
+      <c r="I3" s="92"/>
+      <c r="J3" s="92"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="92"/>
       <c r="P3" s="12"/>
       <c r="Q3" s="13"/>
-      <c r="R3" s="69"/>
-      <c r="S3" s="70"/>
-      <c r="T3" s="70"/>
-      <c r="U3" s="70"/>
-      <c r="V3" s="70"/>
-      <c r="W3" s="70"/>
-      <c r="X3" s="71"/>
+      <c r="R3" s="89"/>
+      <c r="S3" s="90"/>
+      <c r="T3" s="90"/>
+      <c r="U3" s="90"/>
+      <c r="V3" s="90"/>
+      <c r="W3" s="90"/>
+      <c r="X3" s="91"/>
       <c r="Y3" s="12" t="s">
         <v>8</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="57"/>
-      <c r="AB3" s="58"/>
-      <c r="AC3" s="58"/>
-      <c r="AD3" s="58"/>
-      <c r="AE3" s="59"/>
+      <c r="AA3" s="80"/>
+      <c r="AB3" s="81"/>
+      <c r="AC3" s="81"/>
+      <c r="AD3" s="81"/>
+      <c r="AE3" s="82"/>
       <c r="AF3" s="60"/>
       <c r="AG3" s="61"/>
       <c r="AH3" s="61"/>
       <c r="AI3" s="62"/>
     </row>
-    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="5" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B5" s="15" t="s">
         <v>9</v>
       </c>
@@ -5759,8 +5751,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="7" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C7" s="15" t="str">
         <f>$B$5&amp;"2."</f>
         <v>6.2.</v>
@@ -5769,10 +5761,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C8" s="15"/>
     </row>
-    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D9" s="15" t="str">
         <f>$C$7&amp;"1."</f>
         <v>6.2.1.</v>
@@ -5781,7 +5773,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D10" s="15"/>
       <c r="E10" s="15" t="str">
         <f>$D$9&amp;"1."</f>
@@ -5792,18 +5784,18 @@
         <v>ファイル転送（配信）方式概要</v>
       </c>
     </row>
-    <row r="11" spans="1:35" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="F11" s="16" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:35" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:35" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="F12" s="16" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="14" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E14" s="15" t="str">
         <f>$D$9&amp;"2."</f>
         <v>6.2.1.2.</v>
@@ -5813,13 +5805,13 @@
         <v>ファイル転送（配信）方法</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F15" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="17" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="17" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="19"/>
       <c r="F17" s="20" t="s">
         <v>33</v>
@@ -5855,7 +5847,7 @@
       <c r="AG17" s="21"/>
       <c r="AH17" s="22"/>
     </row>
-    <row r="18" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="19"/>
       <c r="F18" s="23" t="s">
         <v>58</v>
@@ -5891,7 +5883,7 @@
       <c r="AG18" s="24"/>
       <c r="AH18" s="25"/>
     </row>
-    <row r="19" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="19"/>
       <c r="F19" s="26"/>
       <c r="G19" s="27"/>
@@ -5925,7 +5917,7 @@
       <c r="AG19" s="27"/>
       <c r="AH19" s="28"/>
     </row>
-    <row r="20" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="19"/>
       <c r="F20" s="26"/>
       <c r="G20" s="27"/>
@@ -5959,7 +5951,7 @@
       <c r="AG20" s="27"/>
       <c r="AH20" s="28"/>
     </row>
-    <row r="21" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="19"/>
       <c r="F21" s="23" t="s">
         <v>59</v>
@@ -5995,7 +5987,7 @@
       <c r="AG21" s="24"/>
       <c r="AH21" s="25"/>
     </row>
-    <row r="22" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="19"/>
       <c r="F22" s="26"/>
       <c r="G22" s="27"/>
@@ -6029,7 +6021,7 @@
       <c r="AG22" s="27"/>
       <c r="AH22" s="28"/>
     </row>
-    <row r="23" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="19"/>
       <c r="F23" s="29"/>
       <c r="G23" s="30"/>
@@ -6063,11 +6055,11 @@
       <c r="AG23" s="30"/>
       <c r="AH23" s="31"/>
     </row>
-    <row r="24" spans="2:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D24" s="18"/>
       <c r="E24" s="50"/>
     </row>
-    <row r="25" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E25" s="15" t="str">
         <f>$D$9&amp;"3."</f>
         <v>6.2.1.3.</v>
@@ -6076,16 +6068,16 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E26" s="15"/>
       <c r="F26" s="16" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E27" s="15"/>
     </row>
-    <row r="28" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D28" s="15" t="str">
         <f>$C$7&amp;"2."</f>
         <v>6.2.2.</v>
@@ -6094,16 +6086,16 @@
         <v>12</v>
       </c>
     </row>
-    <row r="29" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E29" s="15"/>
       <c r="F29" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="30" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E30" s="15"/>
     </row>
-    <row r="31" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E31" s="15"/>
       <c r="F31" s="32" t="s">
         <v>34</v>
@@ -6143,7 +6135,7 @@
       <c r="AG31" s="36"/>
       <c r="AH31" s="37"/>
     </row>
-    <row r="32" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E32" s="15"/>
       <c r="F32" s="38"/>
       <c r="G32" s="38"/>
@@ -6181,7 +6173,7 @@
       <c r="AG32" s="41"/>
       <c r="AH32" s="42"/>
     </row>
-    <row r="33" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E33" s="15"/>
       <c r="F33" s="43"/>
       <c r="G33" s="43"/>
@@ -6221,7 +6213,7 @@
       <c r="AG33" s="48"/>
       <c r="AH33" s="49"/>
     </row>
-    <row r="34" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E34" s="15"/>
       <c r="F34" s="23">
         <v>1</v>
@@ -6247,17 +6239,17 @@
       <c r="Y34" s="24"/>
       <c r="Z34" s="24"/>
       <c r="AA34" s="24"/>
-      <c r="AB34" s="73" t="s">
+      <c r="AB34" s="51" t="s">
         <v>64</v>
       </c>
-      <c r="AC34" s="74"/>
-      <c r="AD34" s="74"/>
-      <c r="AE34" s="74"/>
-      <c r="AF34" s="74"/>
-      <c r="AG34" s="74"/>
-      <c r="AH34" s="75"/>
-    </row>
-    <row r="35" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC34" s="52"/>
+      <c r="AD34" s="52"/>
+      <c r="AE34" s="52"/>
+      <c r="AF34" s="52"/>
+      <c r="AG34" s="52"/>
+      <c r="AH34" s="53"/>
+    </row>
+    <row r="35" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E35" s="15"/>
       <c r="F35" s="26"/>
       <c r="G35" s="26"/>
@@ -6281,15 +6273,15 @@
       <c r="Y35" s="27"/>
       <c r="Z35" s="27"/>
       <c r="AA35" s="27"/>
-      <c r="AB35" s="76"/>
-      <c r="AC35" s="77"/>
-      <c r="AD35" s="77"/>
-      <c r="AE35" s="77"/>
-      <c r="AF35" s="77"/>
-      <c r="AG35" s="77"/>
-      <c r="AH35" s="78"/>
-    </row>
-    <row r="36" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB35" s="54"/>
+      <c r="AC35" s="55"/>
+      <c r="AD35" s="55"/>
+      <c r="AE35" s="55"/>
+      <c r="AF35" s="55"/>
+      <c r="AG35" s="55"/>
+      <c r="AH35" s="56"/>
+    </row>
+    <row r="36" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E36" s="15"/>
       <c r="F36" s="26"/>
       <c r="G36" s="26"/>
@@ -6313,15 +6305,15 @@
       <c r="Y36" s="27"/>
       <c r="Z36" s="27"/>
       <c r="AA36" s="27"/>
-      <c r="AB36" s="76"/>
-      <c r="AC36" s="77"/>
-      <c r="AD36" s="77"/>
-      <c r="AE36" s="77"/>
-      <c r="AF36" s="77"/>
-      <c r="AG36" s="77"/>
-      <c r="AH36" s="78"/>
-    </row>
-    <row r="37" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB36" s="54"/>
+      <c r="AC36" s="55"/>
+      <c r="AD36" s="55"/>
+      <c r="AE36" s="55"/>
+      <c r="AF36" s="55"/>
+      <c r="AG36" s="55"/>
+      <c r="AH36" s="56"/>
+    </row>
+    <row r="37" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E37" s="15"/>
       <c r="F37" s="26"/>
       <c r="G37" s="26"/>
@@ -6345,15 +6337,15 @@
       <c r="Y37" s="27"/>
       <c r="Z37" s="27"/>
       <c r="AA37" s="27"/>
-      <c r="AB37" s="76"/>
-      <c r="AC37" s="77"/>
-      <c r="AD37" s="77"/>
-      <c r="AE37" s="77"/>
-      <c r="AF37" s="77"/>
-      <c r="AG37" s="77"/>
-      <c r="AH37" s="78"/>
-    </row>
-    <row r="38" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB37" s="54"/>
+      <c r="AC37" s="55"/>
+      <c r="AD37" s="55"/>
+      <c r="AE37" s="55"/>
+      <c r="AF37" s="55"/>
+      <c r="AG37" s="55"/>
+      <c r="AH37" s="56"/>
+    </row>
+    <row r="38" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E38" s="15"/>
       <c r="F38" s="26"/>
       <c r="G38" s="26"/>
@@ -6377,15 +6369,15 @@
       <c r="Y38" s="27"/>
       <c r="Z38" s="27"/>
       <c r="AA38" s="27"/>
-      <c r="AB38" s="76"/>
-      <c r="AC38" s="77"/>
-      <c r="AD38" s="77"/>
-      <c r="AE38" s="77"/>
-      <c r="AF38" s="77"/>
-      <c r="AG38" s="77"/>
-      <c r="AH38" s="78"/>
-    </row>
-    <row r="39" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB38" s="54"/>
+      <c r="AC38" s="55"/>
+      <c r="AD38" s="55"/>
+      <c r="AE38" s="55"/>
+      <c r="AF38" s="55"/>
+      <c r="AG38" s="55"/>
+      <c r="AH38" s="56"/>
+    </row>
+    <row r="39" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E39" s="15"/>
       <c r="F39" s="26"/>
       <c r="G39" s="26"/>
@@ -6409,15 +6401,15 @@
       <c r="Y39" s="27"/>
       <c r="Z39" s="27"/>
       <c r="AA39" s="27"/>
-      <c r="AB39" s="76"/>
-      <c r="AC39" s="77"/>
-      <c r="AD39" s="77"/>
-      <c r="AE39" s="77"/>
-      <c r="AF39" s="77"/>
-      <c r="AG39" s="77"/>
-      <c r="AH39" s="78"/>
-    </row>
-    <row r="40" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB39" s="54"/>
+      <c r="AC39" s="55"/>
+      <c r="AD39" s="55"/>
+      <c r="AE39" s="55"/>
+      <c r="AF39" s="55"/>
+      <c r="AG39" s="55"/>
+      <c r="AH39" s="56"/>
+    </row>
+    <row r="40" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E40" s="15"/>
       <c r="F40" s="26"/>
       <c r="G40" s="26"/>
@@ -6441,15 +6433,15 @@
       <c r="Y40" s="27"/>
       <c r="Z40" s="27"/>
       <c r="AA40" s="27"/>
-      <c r="AB40" s="76"/>
-      <c r="AC40" s="77"/>
-      <c r="AD40" s="77"/>
-      <c r="AE40" s="77"/>
-      <c r="AF40" s="77"/>
-      <c r="AG40" s="77"/>
-      <c r="AH40" s="78"/>
-    </row>
-    <row r="41" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB40" s="54"/>
+      <c r="AC40" s="55"/>
+      <c r="AD40" s="55"/>
+      <c r="AE40" s="55"/>
+      <c r="AF40" s="55"/>
+      <c r="AG40" s="55"/>
+      <c r="AH40" s="56"/>
+    </row>
+    <row r="41" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E41" s="15"/>
       <c r="F41" s="26"/>
       <c r="G41" s="26"/>
@@ -6473,15 +6465,15 @@
       <c r="Y41" s="27"/>
       <c r="Z41" s="27"/>
       <c r="AA41" s="27"/>
-      <c r="AB41" s="76"/>
-      <c r="AC41" s="77"/>
-      <c r="AD41" s="77"/>
-      <c r="AE41" s="77"/>
-      <c r="AF41" s="77"/>
-      <c r="AG41" s="77"/>
-      <c r="AH41" s="78"/>
-    </row>
-    <row r="42" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB41" s="54"/>
+      <c r="AC41" s="55"/>
+      <c r="AD41" s="55"/>
+      <c r="AE41" s="55"/>
+      <c r="AF41" s="55"/>
+      <c r="AG41" s="55"/>
+      <c r="AH41" s="56"/>
+    </row>
+    <row r="42" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E42" s="15"/>
       <c r="F42" s="29"/>
       <c r="G42" s="29"/>
@@ -6505,15 +6497,15 @@
       <c r="Y42" s="30"/>
       <c r="Z42" s="30"/>
       <c r="AA42" s="30"/>
-      <c r="AB42" s="79"/>
-      <c r="AC42" s="80"/>
-      <c r="AD42" s="80"/>
-      <c r="AE42" s="80"/>
-      <c r="AF42" s="80"/>
-      <c r="AG42" s="80"/>
-      <c r="AH42" s="81"/>
-    </row>
-    <row r="43" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB42" s="57"/>
+      <c r="AC42" s="58"/>
+      <c r="AD42" s="58"/>
+      <c r="AE42" s="58"/>
+      <c r="AF42" s="58"/>
+      <c r="AG42" s="58"/>
+      <c r="AH42" s="59"/>
+    </row>
+    <row r="43" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E43" s="15"/>
       <c r="F43" s="23">
         <v>2</v>
@@ -6539,17 +6531,17 @@
       <c r="Y43" s="24"/>
       <c r="Z43" s="24"/>
       <c r="AA43" s="24"/>
-      <c r="AB43" s="73" t="s">
+      <c r="AB43" s="51" t="s">
         <v>68</v>
       </c>
-      <c r="AC43" s="74"/>
-      <c r="AD43" s="74"/>
-      <c r="AE43" s="74"/>
-      <c r="AF43" s="74"/>
-      <c r="AG43" s="74"/>
-      <c r="AH43" s="75"/>
-    </row>
-    <row r="44" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC43" s="52"/>
+      <c r="AD43" s="52"/>
+      <c r="AE43" s="52"/>
+      <c r="AF43" s="52"/>
+      <c r="AG43" s="52"/>
+      <c r="AH43" s="53"/>
+    </row>
+    <row r="44" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E44" s="15"/>
       <c r="F44" s="26"/>
       <c r="G44" s="26"/>
@@ -6573,15 +6565,15 @@
       <c r="Y44" s="27"/>
       <c r="Z44" s="27"/>
       <c r="AA44" s="27"/>
-      <c r="AB44" s="76"/>
-      <c r="AC44" s="77"/>
-      <c r="AD44" s="77"/>
-      <c r="AE44" s="77"/>
-      <c r="AF44" s="77"/>
-      <c r="AG44" s="77"/>
-      <c r="AH44" s="78"/>
-    </row>
-    <row r="45" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB44" s="54"/>
+      <c r="AC44" s="55"/>
+      <c r="AD44" s="55"/>
+      <c r="AE44" s="55"/>
+      <c r="AF44" s="55"/>
+      <c r="AG44" s="55"/>
+      <c r="AH44" s="56"/>
+    </row>
+    <row r="45" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E45" s="15"/>
       <c r="F45" s="26"/>
       <c r="G45" s="26"/>
@@ -6605,15 +6597,15 @@
       <c r="Y45" s="27"/>
       <c r="Z45" s="27"/>
       <c r="AA45" s="27"/>
-      <c r="AB45" s="76"/>
-      <c r="AC45" s="77"/>
-      <c r="AD45" s="77"/>
-      <c r="AE45" s="77"/>
-      <c r="AF45" s="77"/>
-      <c r="AG45" s="77"/>
-      <c r="AH45" s="78"/>
-    </row>
-    <row r="46" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB45" s="54"/>
+      <c r="AC45" s="55"/>
+      <c r="AD45" s="55"/>
+      <c r="AE45" s="55"/>
+      <c r="AF45" s="55"/>
+      <c r="AG45" s="55"/>
+      <c r="AH45" s="56"/>
+    </row>
+    <row r="46" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E46" s="15"/>
       <c r="F46" s="26"/>
       <c r="G46" s="26"/>
@@ -6637,15 +6629,15 @@
       <c r="Y46" s="27"/>
       <c r="Z46" s="27"/>
       <c r="AA46" s="27"/>
-      <c r="AB46" s="76"/>
-      <c r="AC46" s="77"/>
-      <c r="AD46" s="77"/>
-      <c r="AE46" s="77"/>
-      <c r="AF46" s="77"/>
-      <c r="AG46" s="77"/>
-      <c r="AH46" s="78"/>
-    </row>
-    <row r="47" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB46" s="54"/>
+      <c r="AC46" s="55"/>
+      <c r="AD46" s="55"/>
+      <c r="AE46" s="55"/>
+      <c r="AF46" s="55"/>
+      <c r="AG46" s="55"/>
+      <c r="AH46" s="56"/>
+    </row>
+    <row r="47" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E47" s="15"/>
       <c r="F47" s="26"/>
       <c r="G47" s="26"/>
@@ -6669,15 +6661,15 @@
       <c r="Y47" s="27"/>
       <c r="Z47" s="27"/>
       <c r="AA47" s="27"/>
-      <c r="AB47" s="76"/>
-      <c r="AC47" s="77"/>
-      <c r="AD47" s="77"/>
-      <c r="AE47" s="77"/>
-      <c r="AF47" s="77"/>
-      <c r="AG47" s="77"/>
-      <c r="AH47" s="78"/>
-    </row>
-    <row r="48" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB47" s="54"/>
+      <c r="AC47" s="55"/>
+      <c r="AD47" s="55"/>
+      <c r="AE47" s="55"/>
+      <c r="AF47" s="55"/>
+      <c r="AG47" s="55"/>
+      <c r="AH47" s="56"/>
+    </row>
+    <row r="48" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E48" s="15"/>
       <c r="F48" s="26"/>
       <c r="G48" s="26"/>
@@ -6701,15 +6693,15 @@
       <c r="Y48" s="27"/>
       <c r="Z48" s="27"/>
       <c r="AA48" s="27"/>
-      <c r="AB48" s="76"/>
-      <c r="AC48" s="77"/>
-      <c r="AD48" s="77"/>
-      <c r="AE48" s="77"/>
-      <c r="AF48" s="77"/>
-      <c r="AG48" s="77"/>
-      <c r="AH48" s="78"/>
-    </row>
-    <row r="49" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB48" s="54"/>
+      <c r="AC48" s="55"/>
+      <c r="AD48" s="55"/>
+      <c r="AE48" s="55"/>
+      <c r="AF48" s="55"/>
+      <c r="AG48" s="55"/>
+      <c r="AH48" s="56"/>
+    </row>
+    <row r="49" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E49" s="15"/>
       <c r="F49" s="26"/>
       <c r="G49" s="26"/>
@@ -6733,15 +6725,15 @@
       <c r="Y49" s="27"/>
       <c r="Z49" s="27"/>
       <c r="AA49" s="27"/>
-      <c r="AB49" s="76"/>
-      <c r="AC49" s="77"/>
-      <c r="AD49" s="77"/>
-      <c r="AE49" s="77"/>
-      <c r="AF49" s="77"/>
-      <c r="AG49" s="77"/>
-      <c r="AH49" s="78"/>
-    </row>
-    <row r="50" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB49" s="54"/>
+      <c r="AC49" s="55"/>
+      <c r="AD49" s="55"/>
+      <c r="AE49" s="55"/>
+      <c r="AF49" s="55"/>
+      <c r="AG49" s="55"/>
+      <c r="AH49" s="56"/>
+    </row>
+    <row r="50" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E50" s="15"/>
       <c r="F50" s="26"/>
       <c r="G50" s="26"/>
@@ -6765,15 +6757,15 @@
       <c r="Y50" s="27"/>
       <c r="Z50" s="27"/>
       <c r="AA50" s="27"/>
-      <c r="AB50" s="76"/>
-      <c r="AC50" s="77"/>
-      <c r="AD50" s="77"/>
-      <c r="AE50" s="77"/>
-      <c r="AF50" s="77"/>
-      <c r="AG50" s="77"/>
-      <c r="AH50" s="78"/>
-    </row>
-    <row r="51" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB50" s="54"/>
+      <c r="AC50" s="55"/>
+      <c r="AD50" s="55"/>
+      <c r="AE50" s="55"/>
+      <c r="AF50" s="55"/>
+      <c r="AG50" s="55"/>
+      <c r="AH50" s="56"/>
+    </row>
+    <row r="51" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E51" s="15"/>
       <c r="F51" s="26"/>
       <c r="G51" s="26"/>
@@ -6797,15 +6789,15 @@
       <c r="Y51" s="27"/>
       <c r="Z51" s="27"/>
       <c r="AA51" s="27"/>
-      <c r="AB51" s="76"/>
-      <c r="AC51" s="77"/>
-      <c r="AD51" s="77"/>
-      <c r="AE51" s="77"/>
-      <c r="AF51" s="77"/>
-      <c r="AG51" s="77"/>
-      <c r="AH51" s="78"/>
-    </row>
-    <row r="52" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB51" s="54"/>
+      <c r="AC51" s="55"/>
+      <c r="AD51" s="55"/>
+      <c r="AE51" s="55"/>
+      <c r="AF51" s="55"/>
+      <c r="AG51" s="55"/>
+      <c r="AH51" s="56"/>
+    </row>
+    <row r="52" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E52" s="15"/>
       <c r="F52" s="26"/>
       <c r="G52" s="26"/>
@@ -6829,15 +6821,15 @@
       <c r="Y52" s="27"/>
       <c r="Z52" s="27"/>
       <c r="AA52" s="27"/>
-      <c r="AB52" s="76"/>
-      <c r="AC52" s="77"/>
-      <c r="AD52" s="77"/>
-      <c r="AE52" s="77"/>
-      <c r="AF52" s="77"/>
-      <c r="AG52" s="77"/>
-      <c r="AH52" s="78"/>
-    </row>
-    <row r="53" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB52" s="54"/>
+      <c r="AC52" s="55"/>
+      <c r="AD52" s="55"/>
+      <c r="AE52" s="55"/>
+      <c r="AF52" s="55"/>
+      <c r="AG52" s="55"/>
+      <c r="AH52" s="56"/>
+    </row>
+    <row r="53" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E53" s="15"/>
       <c r="F53" s="26"/>
       <c r="G53" s="26"/>
@@ -6861,15 +6853,15 @@
       <c r="Y53" s="27"/>
       <c r="Z53" s="27"/>
       <c r="AA53" s="27"/>
-      <c r="AB53" s="76"/>
-      <c r="AC53" s="77"/>
-      <c r="AD53" s="77"/>
-      <c r="AE53" s="77"/>
-      <c r="AF53" s="77"/>
-      <c r="AG53" s="77"/>
-      <c r="AH53" s="78"/>
-    </row>
-    <row r="54" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB53" s="54"/>
+      <c r="AC53" s="55"/>
+      <c r="AD53" s="55"/>
+      <c r="AE53" s="55"/>
+      <c r="AF53" s="55"/>
+      <c r="AG53" s="55"/>
+      <c r="AH53" s="56"/>
+    </row>
+    <row r="54" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E54" s="15"/>
       <c r="F54" s="29"/>
       <c r="G54" s="29"/>
@@ -6893,15 +6885,15 @@
       <c r="Y54" s="30"/>
       <c r="Z54" s="30"/>
       <c r="AA54" s="30"/>
-      <c r="AB54" s="79"/>
-      <c r="AC54" s="80"/>
-      <c r="AD54" s="80"/>
-      <c r="AE54" s="80"/>
-      <c r="AF54" s="80"/>
-      <c r="AG54" s="80"/>
-      <c r="AH54" s="81"/>
-    </row>
-    <row r="55" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB54" s="57"/>
+      <c r="AC54" s="58"/>
+      <c r="AD54" s="58"/>
+      <c r="AE54" s="58"/>
+      <c r="AF54" s="58"/>
+      <c r="AG54" s="58"/>
+      <c r="AH54" s="59"/>
+    </row>
+    <row r="55" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E55" s="15"/>
       <c r="F55" s="23">
         <v>3</v>
@@ -6927,17 +6919,17 @@
       <c r="Y55" s="24"/>
       <c r="Z55" s="24"/>
       <c r="AA55" s="24"/>
-      <c r="AB55" s="73" t="s">
+      <c r="AB55" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="AC55" s="74"/>
-      <c r="AD55" s="74"/>
-      <c r="AE55" s="74"/>
-      <c r="AF55" s="74"/>
-      <c r="AG55" s="74"/>
-      <c r="AH55" s="75"/>
-    </row>
-    <row r="56" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC55" s="52"/>
+      <c r="AD55" s="52"/>
+      <c r="AE55" s="52"/>
+      <c r="AF55" s="52"/>
+      <c r="AG55" s="52"/>
+      <c r="AH55" s="53"/>
+    </row>
+    <row r="56" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E56" s="15"/>
       <c r="F56" s="26"/>
       <c r="G56" s="26"/>
@@ -6961,15 +6953,15 @@
       <c r="Y56" s="27"/>
       <c r="Z56" s="27"/>
       <c r="AA56" s="27"/>
-      <c r="AB56" s="76"/>
-      <c r="AC56" s="77"/>
-      <c r="AD56" s="77"/>
-      <c r="AE56" s="77"/>
-      <c r="AF56" s="77"/>
-      <c r="AG56" s="77"/>
-      <c r="AH56" s="78"/>
-    </row>
-    <row r="57" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB56" s="54"/>
+      <c r="AC56" s="55"/>
+      <c r="AD56" s="55"/>
+      <c r="AE56" s="55"/>
+      <c r="AF56" s="55"/>
+      <c r="AG56" s="55"/>
+      <c r="AH56" s="56"/>
+    </row>
+    <row r="57" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E57" s="15"/>
       <c r="F57" s="26"/>
       <c r="G57" s="26"/>
@@ -6993,15 +6985,15 @@
       <c r="Y57" s="27"/>
       <c r="Z57" s="27"/>
       <c r="AA57" s="27"/>
-      <c r="AB57" s="76"/>
-      <c r="AC57" s="77"/>
-      <c r="AD57" s="77"/>
-      <c r="AE57" s="77"/>
-      <c r="AF57" s="77"/>
-      <c r="AG57" s="77"/>
-      <c r="AH57" s="78"/>
-    </row>
-    <row r="58" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB57" s="54"/>
+      <c r="AC57" s="55"/>
+      <c r="AD57" s="55"/>
+      <c r="AE57" s="55"/>
+      <c r="AF57" s="55"/>
+      <c r="AG57" s="55"/>
+      <c r="AH57" s="56"/>
+    </row>
+    <row r="58" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E58" s="15"/>
       <c r="F58" s="26"/>
       <c r="G58" s="26"/>
@@ -7025,15 +7017,15 @@
       <c r="Y58" s="27"/>
       <c r="Z58" s="27"/>
       <c r="AA58" s="27"/>
-      <c r="AB58" s="76"/>
-      <c r="AC58" s="77"/>
-      <c r="AD58" s="77"/>
-      <c r="AE58" s="77"/>
-      <c r="AF58" s="77"/>
-      <c r="AG58" s="77"/>
-      <c r="AH58" s="78"/>
-    </row>
-    <row r="59" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB58" s="54"/>
+      <c r="AC58" s="55"/>
+      <c r="AD58" s="55"/>
+      <c r="AE58" s="55"/>
+      <c r="AF58" s="55"/>
+      <c r="AG58" s="55"/>
+      <c r="AH58" s="56"/>
+    </row>
+    <row r="59" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E59" s="15"/>
       <c r="F59" s="26"/>
       <c r="G59" s="26"/>
@@ -7057,15 +7049,15 @@
       <c r="Y59" s="27"/>
       <c r="Z59" s="27"/>
       <c r="AA59" s="27"/>
-      <c r="AB59" s="76"/>
-      <c r="AC59" s="77"/>
-      <c r="AD59" s="77"/>
-      <c r="AE59" s="77"/>
-      <c r="AF59" s="77"/>
-      <c r="AG59" s="77"/>
-      <c r="AH59" s="78"/>
-    </row>
-    <row r="60" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB59" s="54"/>
+      <c r="AC59" s="55"/>
+      <c r="AD59" s="55"/>
+      <c r="AE59" s="55"/>
+      <c r="AF59" s="55"/>
+      <c r="AG59" s="55"/>
+      <c r="AH59" s="56"/>
+    </row>
+    <row r="60" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E60" s="15"/>
       <c r="F60" s="26"/>
       <c r="G60" s="26"/>
@@ -7089,15 +7081,15 @@
       <c r="Y60" s="27"/>
       <c r="Z60" s="27"/>
       <c r="AA60" s="27"/>
-      <c r="AB60" s="76"/>
-      <c r="AC60" s="77"/>
-      <c r="AD60" s="77"/>
-      <c r="AE60" s="77"/>
-      <c r="AF60" s="77"/>
-      <c r="AG60" s="77"/>
-      <c r="AH60" s="78"/>
-    </row>
-    <row r="61" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB60" s="54"/>
+      <c r="AC60" s="55"/>
+      <c r="AD60" s="55"/>
+      <c r="AE60" s="55"/>
+      <c r="AF60" s="55"/>
+      <c r="AG60" s="55"/>
+      <c r="AH60" s="56"/>
+    </row>
+    <row r="61" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E61" s="15"/>
       <c r="F61" s="26"/>
       <c r="G61" s="26"/>
@@ -7121,15 +7113,15 @@
       <c r="Y61" s="27"/>
       <c r="Z61" s="27"/>
       <c r="AA61" s="27"/>
-      <c r="AB61" s="76"/>
-      <c r="AC61" s="77"/>
-      <c r="AD61" s="77"/>
-      <c r="AE61" s="77"/>
-      <c r="AF61" s="77"/>
-      <c r="AG61" s="77"/>
-      <c r="AH61" s="78"/>
-    </row>
-    <row r="62" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB61" s="54"/>
+      <c r="AC61" s="55"/>
+      <c r="AD61" s="55"/>
+      <c r="AE61" s="55"/>
+      <c r="AF61" s="55"/>
+      <c r="AG61" s="55"/>
+      <c r="AH61" s="56"/>
+    </row>
+    <row r="62" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E62" s="15"/>
       <c r="F62" s="26"/>
       <c r="G62" s="26"/>
@@ -7153,15 +7145,15 @@
       <c r="Y62" s="27"/>
       <c r="Z62" s="27"/>
       <c r="AA62" s="27"/>
-      <c r="AB62" s="76"/>
-      <c r="AC62" s="77"/>
-      <c r="AD62" s="77"/>
-      <c r="AE62" s="77"/>
-      <c r="AF62" s="77"/>
-      <c r="AG62" s="77"/>
-      <c r="AH62" s="78"/>
-    </row>
-    <row r="63" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB62" s="54"/>
+      <c r="AC62" s="55"/>
+      <c r="AD62" s="55"/>
+      <c r="AE62" s="55"/>
+      <c r="AF62" s="55"/>
+      <c r="AG62" s="55"/>
+      <c r="AH62" s="56"/>
+    </row>
+    <row r="63" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E63" s="15"/>
       <c r="F63" s="26"/>
       <c r="G63" s="26"/>
@@ -7185,15 +7177,15 @@
       <c r="Y63" s="27"/>
       <c r="Z63" s="27"/>
       <c r="AA63" s="27"/>
-      <c r="AB63" s="76"/>
-      <c r="AC63" s="77"/>
-      <c r="AD63" s="77"/>
-      <c r="AE63" s="77"/>
-      <c r="AF63" s="77"/>
-      <c r="AG63" s="77"/>
-      <c r="AH63" s="78"/>
-    </row>
-    <row r="64" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB63" s="54"/>
+      <c r="AC63" s="55"/>
+      <c r="AD63" s="55"/>
+      <c r="AE63" s="55"/>
+      <c r="AF63" s="55"/>
+      <c r="AG63" s="55"/>
+      <c r="AH63" s="56"/>
+    </row>
+    <row r="64" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E64" s="15"/>
       <c r="F64" s="26"/>
       <c r="G64" s="26"/>
@@ -7217,15 +7209,15 @@
       <c r="Y64" s="27"/>
       <c r="Z64" s="27"/>
       <c r="AA64" s="27"/>
-      <c r="AB64" s="76"/>
-      <c r="AC64" s="77"/>
-      <c r="AD64" s="77"/>
-      <c r="AE64" s="77"/>
-      <c r="AF64" s="77"/>
-      <c r="AG64" s="77"/>
-      <c r="AH64" s="78"/>
-    </row>
-    <row r="65" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB64" s="54"/>
+      <c r="AC64" s="55"/>
+      <c r="AD64" s="55"/>
+      <c r="AE64" s="55"/>
+      <c r="AF64" s="55"/>
+      <c r="AG64" s="55"/>
+      <c r="AH64" s="56"/>
+    </row>
+    <row r="65" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E65" s="15"/>
       <c r="F65" s="26"/>
       <c r="G65" s="26"/>
@@ -7249,15 +7241,15 @@
       <c r="Y65" s="27"/>
       <c r="Z65" s="27"/>
       <c r="AA65" s="27"/>
-      <c r="AB65" s="76"/>
-      <c r="AC65" s="77"/>
-      <c r="AD65" s="77"/>
-      <c r="AE65" s="77"/>
-      <c r="AF65" s="77"/>
-      <c r="AG65" s="77"/>
-      <c r="AH65" s="78"/>
-    </row>
-    <row r="66" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB65" s="54"/>
+      <c r="AC65" s="55"/>
+      <c r="AD65" s="55"/>
+      <c r="AE65" s="55"/>
+      <c r="AF65" s="55"/>
+      <c r="AG65" s="55"/>
+      <c r="AH65" s="56"/>
+    </row>
+    <row r="66" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E66" s="15"/>
       <c r="F66" s="26"/>
       <c r="G66" s="26"/>
@@ -7281,15 +7273,15 @@
       <c r="Y66" s="27"/>
       <c r="Z66" s="27"/>
       <c r="AA66" s="27"/>
-      <c r="AB66" s="76"/>
-      <c r="AC66" s="77"/>
-      <c r="AD66" s="77"/>
-      <c r="AE66" s="77"/>
-      <c r="AF66" s="77"/>
-      <c r="AG66" s="77"/>
-      <c r="AH66" s="78"/>
-    </row>
-    <row r="67" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB66" s="54"/>
+      <c r="AC66" s="55"/>
+      <c r="AD66" s="55"/>
+      <c r="AE66" s="55"/>
+      <c r="AF66" s="55"/>
+      <c r="AG66" s="55"/>
+      <c r="AH66" s="56"/>
+    </row>
+    <row r="67" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E67" s="15"/>
       <c r="F67" s="29"/>
       <c r="G67" s="29"/>
@@ -7313,15 +7305,15 @@
       <c r="Y67" s="30"/>
       <c r="Z67" s="30"/>
       <c r="AA67" s="30"/>
-      <c r="AB67" s="79"/>
-      <c r="AC67" s="80"/>
-      <c r="AD67" s="80"/>
-      <c r="AE67" s="80"/>
-      <c r="AF67" s="80"/>
-      <c r="AG67" s="80"/>
-      <c r="AH67" s="81"/>
-    </row>
-    <row r="68" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB67" s="57"/>
+      <c r="AC67" s="58"/>
+      <c r="AD67" s="58"/>
+      <c r="AE67" s="58"/>
+      <c r="AF67" s="58"/>
+      <c r="AG67" s="58"/>
+      <c r="AH67" s="59"/>
+    </row>
+    <row r="68" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E68" s="15"/>
       <c r="F68" s="23">
         <v>4</v>
@@ -7347,17 +7339,17 @@
       <c r="Y68" s="24"/>
       <c r="Z68" s="24"/>
       <c r="AA68" s="24"/>
-      <c r="AB68" s="73" t="s">
+      <c r="AB68" s="51" t="s">
         <v>46</v>
       </c>
-      <c r="AC68" s="82"/>
-      <c r="AD68" s="82"/>
-      <c r="AE68" s="82"/>
-      <c r="AF68" s="82"/>
-      <c r="AG68" s="82"/>
-      <c r="AH68" s="83"/>
-    </row>
-    <row r="69" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC68" s="63"/>
+      <c r="AD68" s="63"/>
+      <c r="AE68" s="63"/>
+      <c r="AF68" s="63"/>
+      <c r="AG68" s="63"/>
+      <c r="AH68" s="64"/>
+    </row>
+    <row r="69" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E69" s="15"/>
       <c r="F69" s="26"/>
       <c r="G69" s="26"/>
@@ -7381,15 +7373,15 @@
       <c r="Y69" s="27"/>
       <c r="Z69" s="27"/>
       <c r="AA69" s="27"/>
-      <c r="AB69" s="84"/>
-      <c r="AC69" s="85"/>
-      <c r="AD69" s="85"/>
-      <c r="AE69" s="85"/>
-      <c r="AF69" s="85"/>
-      <c r="AG69" s="85"/>
-      <c r="AH69" s="86"/>
-    </row>
-    <row r="70" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB69" s="65"/>
+      <c r="AC69" s="66"/>
+      <c r="AD69" s="66"/>
+      <c r="AE69" s="66"/>
+      <c r="AF69" s="66"/>
+      <c r="AG69" s="66"/>
+      <c r="AH69" s="67"/>
+    </row>
+    <row r="70" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E70" s="15"/>
       <c r="F70" s="26"/>
       <c r="G70" s="26"/>
@@ -7413,15 +7405,15 @@
       <c r="Y70" s="27"/>
       <c r="Z70" s="27"/>
       <c r="AA70" s="27"/>
-      <c r="AB70" s="84"/>
-      <c r="AC70" s="85"/>
-      <c r="AD70" s="85"/>
-      <c r="AE70" s="85"/>
-      <c r="AF70" s="85"/>
-      <c r="AG70" s="85"/>
-      <c r="AH70" s="86"/>
-    </row>
-    <row r="71" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB70" s="65"/>
+      <c r="AC70" s="66"/>
+      <c r="AD70" s="66"/>
+      <c r="AE70" s="66"/>
+      <c r="AF70" s="66"/>
+      <c r="AG70" s="66"/>
+      <c r="AH70" s="67"/>
+    </row>
+    <row r="71" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E71" s="15"/>
       <c r="F71" s="26"/>
       <c r="G71" s="26"/>
@@ -7445,15 +7437,15 @@
       <c r="Y71" s="27"/>
       <c r="Z71" s="27"/>
       <c r="AA71" s="27"/>
-      <c r="AB71" s="84"/>
-      <c r="AC71" s="85"/>
-      <c r="AD71" s="85"/>
-      <c r="AE71" s="85"/>
-      <c r="AF71" s="85"/>
-      <c r="AG71" s="85"/>
-      <c r="AH71" s="86"/>
-    </row>
-    <row r="72" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB71" s="65"/>
+      <c r="AC71" s="66"/>
+      <c r="AD71" s="66"/>
+      <c r="AE71" s="66"/>
+      <c r="AF71" s="66"/>
+      <c r="AG71" s="66"/>
+      <c r="AH71" s="67"/>
+    </row>
+    <row r="72" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E72" s="15"/>
       <c r="F72" s="26"/>
       <c r="G72" s="26"/>
@@ -7477,15 +7469,15 @@
       <c r="Y72" s="27"/>
       <c r="Z72" s="27"/>
       <c r="AA72" s="27"/>
-      <c r="AB72" s="84"/>
-      <c r="AC72" s="85"/>
-      <c r="AD72" s="85"/>
-      <c r="AE72" s="85"/>
-      <c r="AF72" s="85"/>
-      <c r="AG72" s="85"/>
-      <c r="AH72" s="86"/>
-    </row>
-    <row r="73" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB72" s="65"/>
+      <c r="AC72" s="66"/>
+      <c r="AD72" s="66"/>
+      <c r="AE72" s="66"/>
+      <c r="AF72" s="66"/>
+      <c r="AG72" s="66"/>
+      <c r="AH72" s="67"/>
+    </row>
+    <row r="73" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E73" s="15"/>
       <c r="F73" s="26"/>
       <c r="G73" s="26"/>
@@ -7509,15 +7501,15 @@
       <c r="Y73" s="27"/>
       <c r="Z73" s="27"/>
       <c r="AA73" s="27"/>
-      <c r="AB73" s="84"/>
-      <c r="AC73" s="85"/>
-      <c r="AD73" s="85"/>
-      <c r="AE73" s="85"/>
-      <c r="AF73" s="85"/>
-      <c r="AG73" s="85"/>
-      <c r="AH73" s="86"/>
-    </row>
-    <row r="74" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB73" s="65"/>
+      <c r="AC73" s="66"/>
+      <c r="AD73" s="66"/>
+      <c r="AE73" s="66"/>
+      <c r="AF73" s="66"/>
+      <c r="AG73" s="66"/>
+      <c r="AH73" s="67"/>
+    </row>
+    <row r="74" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E74" s="15"/>
       <c r="F74" s="26"/>
       <c r="G74" s="26"/>
@@ -7541,15 +7533,15 @@
       <c r="Y74" s="27"/>
       <c r="Z74" s="27"/>
       <c r="AA74" s="27"/>
-      <c r="AB74" s="84"/>
-      <c r="AC74" s="85"/>
-      <c r="AD74" s="85"/>
-      <c r="AE74" s="85"/>
-      <c r="AF74" s="85"/>
-      <c r="AG74" s="85"/>
-      <c r="AH74" s="86"/>
-    </row>
-    <row r="75" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB74" s="65"/>
+      <c r="AC74" s="66"/>
+      <c r="AD74" s="66"/>
+      <c r="AE74" s="66"/>
+      <c r="AF74" s="66"/>
+      <c r="AG74" s="66"/>
+      <c r="AH74" s="67"/>
+    </row>
+    <row r="75" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E75" s="15"/>
       <c r="F75" s="26"/>
       <c r="G75" s="26"/>
@@ -7573,15 +7565,15 @@
       <c r="Y75" s="27"/>
       <c r="Z75" s="27"/>
       <c r="AA75" s="27"/>
-      <c r="AB75" s="84"/>
-      <c r="AC75" s="85"/>
-      <c r="AD75" s="85"/>
-      <c r="AE75" s="85"/>
-      <c r="AF75" s="85"/>
-      <c r="AG75" s="85"/>
-      <c r="AH75" s="86"/>
-    </row>
-    <row r="76" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB75" s="65"/>
+      <c r="AC75" s="66"/>
+      <c r="AD75" s="66"/>
+      <c r="AE75" s="66"/>
+      <c r="AF75" s="66"/>
+      <c r="AG75" s="66"/>
+      <c r="AH75" s="67"/>
+    </row>
+    <row r="76" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E76" s="15"/>
       <c r="F76" s="26"/>
       <c r="G76" s="26"/>
@@ -7605,15 +7597,15 @@
       <c r="Y76" s="27"/>
       <c r="Z76" s="27"/>
       <c r="AA76" s="27"/>
-      <c r="AB76" s="84"/>
-      <c r="AC76" s="85"/>
-      <c r="AD76" s="85"/>
-      <c r="AE76" s="85"/>
-      <c r="AF76" s="85"/>
-      <c r="AG76" s="85"/>
-      <c r="AH76" s="86"/>
-    </row>
-    <row r="77" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB76" s="65"/>
+      <c r="AC76" s="66"/>
+      <c r="AD76" s="66"/>
+      <c r="AE76" s="66"/>
+      <c r="AF76" s="66"/>
+      <c r="AG76" s="66"/>
+      <c r="AH76" s="67"/>
+    </row>
+    <row r="77" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E77" s="15"/>
       <c r="F77" s="29"/>
       <c r="G77" s="29"/>
@@ -7637,15 +7629,15 @@
       <c r="Y77" s="30"/>
       <c r="Z77" s="30"/>
       <c r="AA77" s="30"/>
-      <c r="AB77" s="87"/>
-      <c r="AC77" s="88"/>
-      <c r="AD77" s="88"/>
-      <c r="AE77" s="88"/>
-      <c r="AF77" s="88"/>
-      <c r="AG77" s="88"/>
-      <c r="AH77" s="89"/>
-    </row>
-    <row r="78" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB77" s="68"/>
+      <c r="AC77" s="69"/>
+      <c r="AD77" s="69"/>
+      <c r="AE77" s="69"/>
+      <c r="AF77" s="69"/>
+      <c r="AG77" s="69"/>
+      <c r="AH77" s="70"/>
+    </row>
+    <row r="78" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E78" s="15"/>
       <c r="F78" s="23">
         <v>5</v>
@@ -7671,17 +7663,17 @@
       <c r="Y78" s="24"/>
       <c r="Z78" s="24"/>
       <c r="AA78" s="24"/>
-      <c r="AB78" s="73" t="s">
+      <c r="AB78" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="AC78" s="74"/>
-      <c r="AD78" s="74"/>
-      <c r="AE78" s="74"/>
-      <c r="AF78" s="74"/>
-      <c r="AG78" s="74"/>
-      <c r="AH78" s="75"/>
-    </row>
-    <row r="79" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC78" s="52"/>
+      <c r="AD78" s="52"/>
+      <c r="AE78" s="52"/>
+      <c r="AF78" s="52"/>
+      <c r="AG78" s="52"/>
+      <c r="AH78" s="53"/>
+    </row>
+    <row r="79" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E79" s="15"/>
       <c r="F79" s="26"/>
       <c r="G79" s="26"/>
@@ -7705,15 +7697,15 @@
       <c r="Y79" s="27"/>
       <c r="Z79" s="27"/>
       <c r="AA79" s="27"/>
-      <c r="AB79" s="76"/>
-      <c r="AC79" s="77"/>
-      <c r="AD79" s="77"/>
-      <c r="AE79" s="77"/>
-      <c r="AF79" s="77"/>
-      <c r="AG79" s="77"/>
-      <c r="AH79" s="78"/>
-    </row>
-    <row r="80" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB79" s="54"/>
+      <c r="AC79" s="55"/>
+      <c r="AD79" s="55"/>
+      <c r="AE79" s="55"/>
+      <c r="AF79" s="55"/>
+      <c r="AG79" s="55"/>
+      <c r="AH79" s="56"/>
+    </row>
+    <row r="80" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E80" s="15"/>
       <c r="F80" s="26"/>
       <c r="G80" s="26"/>
@@ -7737,15 +7729,15 @@
       <c r="Y80" s="27"/>
       <c r="Z80" s="27"/>
       <c r="AA80" s="27"/>
-      <c r="AB80" s="76"/>
-      <c r="AC80" s="77"/>
-      <c r="AD80" s="77"/>
-      <c r="AE80" s="77"/>
-      <c r="AF80" s="77"/>
-      <c r="AG80" s="77"/>
-      <c r="AH80" s="78"/>
-    </row>
-    <row r="81" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB80" s="54"/>
+      <c r="AC80" s="55"/>
+      <c r="AD80" s="55"/>
+      <c r="AE80" s="55"/>
+      <c r="AF80" s="55"/>
+      <c r="AG80" s="55"/>
+      <c r="AH80" s="56"/>
+    </row>
+    <row r="81" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E81" s="15"/>
       <c r="F81" s="26"/>
       <c r="G81" s="26"/>
@@ -7769,15 +7761,15 @@
       <c r="Y81" s="27"/>
       <c r="Z81" s="27"/>
       <c r="AA81" s="27"/>
-      <c r="AB81" s="76"/>
-      <c r="AC81" s="77"/>
-      <c r="AD81" s="77"/>
-      <c r="AE81" s="77"/>
-      <c r="AF81" s="77"/>
-      <c r="AG81" s="77"/>
-      <c r="AH81" s="78"/>
-    </row>
-    <row r="82" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB81" s="54"/>
+      <c r="AC81" s="55"/>
+      <c r="AD81" s="55"/>
+      <c r="AE81" s="55"/>
+      <c r="AF81" s="55"/>
+      <c r="AG81" s="55"/>
+      <c r="AH81" s="56"/>
+    </row>
+    <row r="82" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E82" s="15"/>
       <c r="F82" s="26"/>
       <c r="G82" s="26"/>
@@ -7801,15 +7793,15 @@
       <c r="Y82" s="27"/>
       <c r="Z82" s="27"/>
       <c r="AA82" s="27"/>
-      <c r="AB82" s="76"/>
-      <c r="AC82" s="77"/>
-      <c r="AD82" s="77"/>
-      <c r="AE82" s="77"/>
-      <c r="AF82" s="77"/>
-      <c r="AG82" s="77"/>
-      <c r="AH82" s="78"/>
-    </row>
-    <row r="83" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB82" s="54"/>
+      <c r="AC82" s="55"/>
+      <c r="AD82" s="55"/>
+      <c r="AE82" s="55"/>
+      <c r="AF82" s="55"/>
+      <c r="AG82" s="55"/>
+      <c r="AH82" s="56"/>
+    </row>
+    <row r="83" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E83" s="15"/>
       <c r="F83" s="26"/>
       <c r="G83" s="26"/>
@@ -7833,15 +7825,15 @@
       <c r="Y83" s="27"/>
       <c r="Z83" s="27"/>
       <c r="AA83" s="27"/>
-      <c r="AB83" s="76"/>
-      <c r="AC83" s="77"/>
-      <c r="AD83" s="77"/>
-      <c r="AE83" s="77"/>
-      <c r="AF83" s="77"/>
-      <c r="AG83" s="77"/>
-      <c r="AH83" s="78"/>
-    </row>
-    <row r="84" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB83" s="54"/>
+      <c r="AC83" s="55"/>
+      <c r="AD83" s="55"/>
+      <c r="AE83" s="55"/>
+      <c r="AF83" s="55"/>
+      <c r="AG83" s="55"/>
+      <c r="AH83" s="56"/>
+    </row>
+    <row r="84" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E84" s="15"/>
       <c r="F84" s="26"/>
       <c r="G84" s="26"/>
@@ -7865,15 +7857,15 @@
       <c r="Y84" s="27"/>
       <c r="Z84" s="27"/>
       <c r="AA84" s="27"/>
-      <c r="AB84" s="76"/>
-      <c r="AC84" s="77"/>
-      <c r="AD84" s="77"/>
-      <c r="AE84" s="77"/>
-      <c r="AF84" s="77"/>
-      <c r="AG84" s="77"/>
-      <c r="AH84" s="78"/>
-    </row>
-    <row r="85" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB84" s="54"/>
+      <c r="AC84" s="55"/>
+      <c r="AD84" s="55"/>
+      <c r="AE84" s="55"/>
+      <c r="AF84" s="55"/>
+      <c r="AG84" s="55"/>
+      <c r="AH84" s="56"/>
+    </row>
+    <row r="85" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E85" s="15"/>
       <c r="F85" s="26"/>
       <c r="G85" s="26"/>
@@ -7897,15 +7889,15 @@
       <c r="Y85" s="27"/>
       <c r="Z85" s="27"/>
       <c r="AA85" s="27"/>
-      <c r="AB85" s="76"/>
-      <c r="AC85" s="77"/>
-      <c r="AD85" s="77"/>
-      <c r="AE85" s="77"/>
-      <c r="AF85" s="77"/>
-      <c r="AG85" s="77"/>
-      <c r="AH85" s="78"/>
-    </row>
-    <row r="86" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB85" s="54"/>
+      <c r="AC85" s="55"/>
+      <c r="AD85" s="55"/>
+      <c r="AE85" s="55"/>
+      <c r="AF85" s="55"/>
+      <c r="AG85" s="55"/>
+      <c r="AH85" s="56"/>
+    </row>
+    <row r="86" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E86" s="15"/>
       <c r="F86" s="26"/>
       <c r="G86" s="26"/>
@@ -7929,15 +7921,15 @@
       <c r="Y86" s="27"/>
       <c r="Z86" s="27"/>
       <c r="AA86" s="27"/>
-      <c r="AB86" s="76"/>
-      <c r="AC86" s="77"/>
-      <c r="AD86" s="77"/>
-      <c r="AE86" s="77"/>
-      <c r="AF86" s="77"/>
-      <c r="AG86" s="77"/>
-      <c r="AH86" s="78"/>
-    </row>
-    <row r="87" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB86" s="54"/>
+      <c r="AC86" s="55"/>
+      <c r="AD86" s="55"/>
+      <c r="AE86" s="55"/>
+      <c r="AF86" s="55"/>
+      <c r="AG86" s="55"/>
+      <c r="AH86" s="56"/>
+    </row>
+    <row r="87" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E87" s="15"/>
       <c r="F87" s="26"/>
       <c r="G87" s="26"/>
@@ -7961,15 +7953,15 @@
       <c r="Y87" s="27"/>
       <c r="Z87" s="27"/>
       <c r="AA87" s="27"/>
-      <c r="AB87" s="76"/>
-      <c r="AC87" s="77"/>
-      <c r="AD87" s="77"/>
-      <c r="AE87" s="77"/>
-      <c r="AF87" s="77"/>
-      <c r="AG87" s="77"/>
-      <c r="AH87" s="78"/>
-    </row>
-    <row r="88" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB87" s="54"/>
+      <c r="AC87" s="55"/>
+      <c r="AD87" s="55"/>
+      <c r="AE87" s="55"/>
+      <c r="AF87" s="55"/>
+      <c r="AG87" s="55"/>
+      <c r="AH87" s="56"/>
+    </row>
+    <row r="88" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E88" s="15"/>
       <c r="F88" s="26"/>
       <c r="G88" s="26"/>
@@ -7993,15 +7985,15 @@
       <c r="Y88" s="27"/>
       <c r="Z88" s="27"/>
       <c r="AA88" s="27"/>
-      <c r="AB88" s="76"/>
-      <c r="AC88" s="77"/>
-      <c r="AD88" s="77"/>
-      <c r="AE88" s="77"/>
-      <c r="AF88" s="77"/>
-      <c r="AG88" s="77"/>
-      <c r="AH88" s="78"/>
-    </row>
-    <row r="89" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB88" s="54"/>
+      <c r="AC88" s="55"/>
+      <c r="AD88" s="55"/>
+      <c r="AE88" s="55"/>
+      <c r="AF88" s="55"/>
+      <c r="AG88" s="55"/>
+      <c r="AH88" s="56"/>
+    </row>
+    <row r="89" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E89" s="15"/>
       <c r="F89" s="26"/>
       <c r="G89" s="26"/>
@@ -8025,15 +8017,15 @@
       <c r="Y89" s="27"/>
       <c r="Z89" s="27"/>
       <c r="AA89" s="27"/>
-      <c r="AB89" s="76"/>
-      <c r="AC89" s="77"/>
-      <c r="AD89" s="77"/>
-      <c r="AE89" s="77"/>
-      <c r="AF89" s="77"/>
-      <c r="AG89" s="77"/>
-      <c r="AH89" s="78"/>
-    </row>
-    <row r="90" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB89" s="54"/>
+      <c r="AC89" s="55"/>
+      <c r="AD89" s="55"/>
+      <c r="AE89" s="55"/>
+      <c r="AF89" s="55"/>
+      <c r="AG89" s="55"/>
+      <c r="AH89" s="56"/>
+    </row>
+    <row r="90" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E90" s="15"/>
       <c r="F90" s="26"/>
       <c r="G90" s="26"/>
@@ -8057,15 +8049,15 @@
       <c r="Y90" s="27"/>
       <c r="Z90" s="27"/>
       <c r="AA90" s="27"/>
-      <c r="AB90" s="76"/>
-      <c r="AC90" s="77"/>
-      <c r="AD90" s="77"/>
-      <c r="AE90" s="77"/>
-      <c r="AF90" s="77"/>
-      <c r="AG90" s="77"/>
-      <c r="AH90" s="78"/>
-    </row>
-    <row r="91" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB90" s="54"/>
+      <c r="AC90" s="55"/>
+      <c r="AD90" s="55"/>
+      <c r="AE90" s="55"/>
+      <c r="AF90" s="55"/>
+      <c r="AG90" s="55"/>
+      <c r="AH90" s="56"/>
+    </row>
+    <row r="91" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E91" s="15"/>
       <c r="F91" s="23">
         <v>6</v>
@@ -8091,17 +8083,17 @@
       <c r="Y91" s="24"/>
       <c r="Z91" s="24"/>
       <c r="AA91" s="24"/>
-      <c r="AB91" s="73" t="s">
+      <c r="AB91" s="51" t="s">
         <v>52</v>
       </c>
-      <c r="AC91" s="74"/>
-      <c r="AD91" s="74"/>
-      <c r="AE91" s="74"/>
-      <c r="AF91" s="74"/>
-      <c r="AG91" s="74"/>
-      <c r="AH91" s="75"/>
-    </row>
-    <row r="92" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC91" s="52"/>
+      <c r="AD91" s="52"/>
+      <c r="AE91" s="52"/>
+      <c r="AF91" s="52"/>
+      <c r="AG91" s="52"/>
+      <c r="AH91" s="53"/>
+    </row>
+    <row r="92" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E92" s="15"/>
       <c r="F92" s="26"/>
       <c r="G92" s="26"/>
@@ -8125,15 +8117,15 @@
       <c r="Y92" s="27"/>
       <c r="Z92" s="27"/>
       <c r="AA92" s="27"/>
-      <c r="AB92" s="76"/>
-      <c r="AC92" s="77"/>
-      <c r="AD92" s="77"/>
-      <c r="AE92" s="77"/>
-      <c r="AF92" s="77"/>
-      <c r="AG92" s="77"/>
-      <c r="AH92" s="78"/>
-    </row>
-    <row r="93" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB92" s="54"/>
+      <c r="AC92" s="55"/>
+      <c r="AD92" s="55"/>
+      <c r="AE92" s="55"/>
+      <c r="AF92" s="55"/>
+      <c r="AG92" s="55"/>
+      <c r="AH92" s="56"/>
+    </row>
+    <row r="93" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E93" s="15"/>
       <c r="F93" s="26"/>
       <c r="G93" s="26"/>
@@ -8157,15 +8149,15 @@
       <c r="Y93" s="27"/>
       <c r="Z93" s="27"/>
       <c r="AA93" s="27"/>
-      <c r="AB93" s="76"/>
-      <c r="AC93" s="77"/>
-      <c r="AD93" s="77"/>
-      <c r="AE93" s="77"/>
-      <c r="AF93" s="77"/>
-      <c r="AG93" s="77"/>
-      <c r="AH93" s="78"/>
-    </row>
-    <row r="94" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB93" s="54"/>
+      <c r="AC93" s="55"/>
+      <c r="AD93" s="55"/>
+      <c r="AE93" s="55"/>
+      <c r="AF93" s="55"/>
+      <c r="AG93" s="55"/>
+      <c r="AH93" s="56"/>
+    </row>
+    <row r="94" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E94" s="15"/>
       <c r="F94" s="26"/>
       <c r="G94" s="26"/>
@@ -8189,15 +8181,15 @@
       <c r="Y94" s="27"/>
       <c r="Z94" s="27"/>
       <c r="AA94" s="27"/>
-      <c r="AB94" s="76"/>
-      <c r="AC94" s="77"/>
-      <c r="AD94" s="77"/>
-      <c r="AE94" s="77"/>
-      <c r="AF94" s="77"/>
-      <c r="AG94" s="77"/>
-      <c r="AH94" s="78"/>
-    </row>
-    <row r="95" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB94" s="54"/>
+      <c r="AC94" s="55"/>
+      <c r="AD94" s="55"/>
+      <c r="AE94" s="55"/>
+      <c r="AF94" s="55"/>
+      <c r="AG94" s="55"/>
+      <c r="AH94" s="56"/>
+    </row>
+    <row r="95" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E95" s="15"/>
       <c r="F95" s="26"/>
       <c r="G95" s="26"/>
@@ -8221,15 +8213,15 @@
       <c r="Y95" s="27"/>
       <c r="Z95" s="27"/>
       <c r="AA95" s="27"/>
-      <c r="AB95" s="76"/>
-      <c r="AC95" s="77"/>
-      <c r="AD95" s="77"/>
-      <c r="AE95" s="77"/>
-      <c r="AF95" s="77"/>
-      <c r="AG95" s="77"/>
-      <c r="AH95" s="78"/>
-    </row>
-    <row r="96" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB95" s="54"/>
+      <c r="AC95" s="55"/>
+      <c r="AD95" s="55"/>
+      <c r="AE95" s="55"/>
+      <c r="AF95" s="55"/>
+      <c r="AG95" s="55"/>
+      <c r="AH95" s="56"/>
+    </row>
+    <row r="96" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E96" s="15"/>
       <c r="F96" s="26"/>
       <c r="G96" s="26"/>
@@ -8253,15 +8245,15 @@
       <c r="Y96" s="27"/>
       <c r="Z96" s="27"/>
       <c r="AA96" s="27"/>
-      <c r="AB96" s="76"/>
-      <c r="AC96" s="77"/>
-      <c r="AD96" s="77"/>
-      <c r="AE96" s="77"/>
-      <c r="AF96" s="77"/>
-      <c r="AG96" s="77"/>
-      <c r="AH96" s="78"/>
-    </row>
-    <row r="97" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB96" s="54"/>
+      <c r="AC96" s="55"/>
+      <c r="AD96" s="55"/>
+      <c r="AE96" s="55"/>
+      <c r="AF96" s="55"/>
+      <c r="AG96" s="55"/>
+      <c r="AH96" s="56"/>
+    </row>
+    <row r="97" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E97" s="15"/>
       <c r="F97" s="26"/>
       <c r="G97" s="26"/>
@@ -8285,15 +8277,15 @@
       <c r="Y97" s="27"/>
       <c r="Z97" s="27"/>
       <c r="AA97" s="27"/>
-      <c r="AB97" s="76"/>
-      <c r="AC97" s="77"/>
-      <c r="AD97" s="77"/>
-      <c r="AE97" s="77"/>
-      <c r="AF97" s="77"/>
-      <c r="AG97" s="77"/>
-      <c r="AH97" s="78"/>
-    </row>
-    <row r="98" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB97" s="54"/>
+      <c r="AC97" s="55"/>
+      <c r="AD97" s="55"/>
+      <c r="AE97" s="55"/>
+      <c r="AF97" s="55"/>
+      <c r="AG97" s="55"/>
+      <c r="AH97" s="56"/>
+    </row>
+    <row r="98" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E98" s="15"/>
       <c r="F98" s="26"/>
       <c r="G98" s="26"/>
@@ -8317,15 +8309,15 @@
       <c r="Y98" s="27"/>
       <c r="Z98" s="27"/>
       <c r="AA98" s="27"/>
-      <c r="AB98" s="76"/>
-      <c r="AC98" s="77"/>
-      <c r="AD98" s="77"/>
-      <c r="AE98" s="77"/>
-      <c r="AF98" s="77"/>
-      <c r="AG98" s="77"/>
-      <c r="AH98" s="78"/>
-    </row>
-    <row r="99" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB98" s="54"/>
+      <c r="AC98" s="55"/>
+      <c r="AD98" s="55"/>
+      <c r="AE98" s="55"/>
+      <c r="AF98" s="55"/>
+      <c r="AG98" s="55"/>
+      <c r="AH98" s="56"/>
+    </row>
+    <row r="99" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E99" s="15"/>
       <c r="F99" s="26"/>
       <c r="G99" s="26"/>
@@ -8349,15 +8341,15 @@
       <c r="Y99" s="27"/>
       <c r="Z99" s="27"/>
       <c r="AA99" s="27"/>
-      <c r="AB99" s="76"/>
-      <c r="AC99" s="77"/>
-      <c r="AD99" s="77"/>
-      <c r="AE99" s="77"/>
-      <c r="AF99" s="77"/>
-      <c r="AG99" s="77"/>
-      <c r="AH99" s="78"/>
-    </row>
-    <row r="100" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB99" s="54"/>
+      <c r="AC99" s="55"/>
+      <c r="AD99" s="55"/>
+      <c r="AE99" s="55"/>
+      <c r="AF99" s="55"/>
+      <c r="AG99" s="55"/>
+      <c r="AH99" s="56"/>
+    </row>
+    <row r="100" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E100" s="15"/>
       <c r="F100" s="26"/>
       <c r="G100" s="26"/>
@@ -8381,15 +8373,15 @@
       <c r="Y100" s="27"/>
       <c r="Z100" s="27"/>
       <c r="AA100" s="27"/>
-      <c r="AB100" s="76"/>
-      <c r="AC100" s="77"/>
-      <c r="AD100" s="77"/>
-      <c r="AE100" s="77"/>
-      <c r="AF100" s="77"/>
-      <c r="AG100" s="77"/>
-      <c r="AH100" s="78"/>
-    </row>
-    <row r="101" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB100" s="54"/>
+      <c r="AC100" s="55"/>
+      <c r="AD100" s="55"/>
+      <c r="AE100" s="55"/>
+      <c r="AF100" s="55"/>
+      <c r="AG100" s="55"/>
+      <c r="AH100" s="56"/>
+    </row>
+    <row r="101" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E101" s="15"/>
       <c r="F101" s="26"/>
       <c r="G101" s="26"/>
@@ -8413,15 +8405,15 @@
       <c r="Y101" s="27"/>
       <c r="Z101" s="27"/>
       <c r="AA101" s="27"/>
-      <c r="AB101" s="76"/>
-      <c r="AC101" s="77"/>
-      <c r="AD101" s="77"/>
-      <c r="AE101" s="77"/>
-      <c r="AF101" s="77"/>
-      <c r="AG101" s="77"/>
-      <c r="AH101" s="78"/>
-    </row>
-    <row r="102" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB101" s="54"/>
+      <c r="AC101" s="55"/>
+      <c r="AD101" s="55"/>
+      <c r="AE101" s="55"/>
+      <c r="AF101" s="55"/>
+      <c r="AG101" s="55"/>
+      <c r="AH101" s="56"/>
+    </row>
+    <row r="102" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E102" s="15"/>
       <c r="F102" s="29"/>
       <c r="G102" s="29"/>
@@ -8445,15 +8437,15 @@
       <c r="Y102" s="30"/>
       <c r="Z102" s="30"/>
       <c r="AA102" s="30"/>
-      <c r="AB102" s="79"/>
-      <c r="AC102" s="80"/>
-      <c r="AD102" s="80"/>
-      <c r="AE102" s="80"/>
-      <c r="AF102" s="80"/>
-      <c r="AG102" s="80"/>
-      <c r="AH102" s="81"/>
-    </row>
-    <row r="103" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB102" s="57"/>
+      <c r="AC102" s="58"/>
+      <c r="AD102" s="58"/>
+      <c r="AE102" s="58"/>
+      <c r="AF102" s="58"/>
+      <c r="AG102" s="58"/>
+      <c r="AH102" s="59"/>
+    </row>
+    <row r="103" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E103" s="15"/>
       <c r="F103" s="23">
         <v>7</v>
@@ -8479,17 +8471,17 @@
       <c r="Y103" s="24"/>
       <c r="Z103" s="24"/>
       <c r="AA103" s="24"/>
-      <c r="AB103" s="73" t="s">
+      <c r="AB103" s="51" t="s">
         <v>53</v>
       </c>
-      <c r="AC103" s="74"/>
-      <c r="AD103" s="74"/>
-      <c r="AE103" s="74"/>
-      <c r="AF103" s="74"/>
-      <c r="AG103" s="74"/>
-      <c r="AH103" s="75"/>
-    </row>
-    <row r="104" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC103" s="52"/>
+      <c r="AD103" s="52"/>
+      <c r="AE103" s="52"/>
+      <c r="AF103" s="52"/>
+      <c r="AG103" s="52"/>
+      <c r="AH103" s="53"/>
+    </row>
+    <row r="104" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E104" s="15"/>
       <c r="F104" s="26"/>
       <c r="G104" s="26"/>
@@ -8513,15 +8505,15 @@
       <c r="Y104" s="27"/>
       <c r="Z104" s="27"/>
       <c r="AA104" s="27"/>
-      <c r="AB104" s="76"/>
-      <c r="AC104" s="77"/>
-      <c r="AD104" s="77"/>
-      <c r="AE104" s="77"/>
-      <c r="AF104" s="77"/>
-      <c r="AG104" s="77"/>
-      <c r="AH104" s="78"/>
-    </row>
-    <row r="105" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB104" s="54"/>
+      <c r="AC104" s="55"/>
+      <c r="AD104" s="55"/>
+      <c r="AE104" s="55"/>
+      <c r="AF104" s="55"/>
+      <c r="AG104" s="55"/>
+      <c r="AH104" s="56"/>
+    </row>
+    <row r="105" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E105" s="15"/>
       <c r="F105" s="26"/>
       <c r="G105" s="26"/>
@@ -8545,15 +8537,15 @@
       <c r="Y105" s="27"/>
       <c r="Z105" s="27"/>
       <c r="AA105" s="27"/>
-      <c r="AB105" s="76"/>
-      <c r="AC105" s="77"/>
-      <c r="AD105" s="77"/>
-      <c r="AE105" s="77"/>
-      <c r="AF105" s="77"/>
-      <c r="AG105" s="77"/>
-      <c r="AH105" s="78"/>
-    </row>
-    <row r="106" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB105" s="54"/>
+      <c r="AC105" s="55"/>
+      <c r="AD105" s="55"/>
+      <c r="AE105" s="55"/>
+      <c r="AF105" s="55"/>
+      <c r="AG105" s="55"/>
+      <c r="AH105" s="56"/>
+    </row>
+    <row r="106" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E106" s="15"/>
       <c r="F106" s="26"/>
       <c r="G106" s="26"/>
@@ -8577,15 +8569,15 @@
       <c r="Y106" s="27"/>
       <c r="Z106" s="27"/>
       <c r="AA106" s="27"/>
-      <c r="AB106" s="76"/>
-      <c r="AC106" s="77"/>
-      <c r="AD106" s="77"/>
-      <c r="AE106" s="77"/>
-      <c r="AF106" s="77"/>
-      <c r="AG106" s="77"/>
-      <c r="AH106" s="78"/>
-    </row>
-    <row r="107" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB106" s="54"/>
+      <c r="AC106" s="55"/>
+      <c r="AD106" s="55"/>
+      <c r="AE106" s="55"/>
+      <c r="AF106" s="55"/>
+      <c r="AG106" s="55"/>
+      <c r="AH106" s="56"/>
+    </row>
+    <row r="107" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E107" s="15"/>
       <c r="F107" s="26"/>
       <c r="G107" s="26"/>
@@ -8609,15 +8601,15 @@
       <c r="Y107" s="27"/>
       <c r="Z107" s="27"/>
       <c r="AA107" s="27"/>
-      <c r="AB107" s="76"/>
-      <c r="AC107" s="77"/>
-      <c r="AD107" s="77"/>
-      <c r="AE107" s="77"/>
-      <c r="AF107" s="77"/>
-      <c r="AG107" s="77"/>
-      <c r="AH107" s="78"/>
-    </row>
-    <row r="108" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB107" s="54"/>
+      <c r="AC107" s="55"/>
+      <c r="AD107" s="55"/>
+      <c r="AE107" s="55"/>
+      <c r="AF107" s="55"/>
+      <c r="AG107" s="55"/>
+      <c r="AH107" s="56"/>
+    </row>
+    <row r="108" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E108" s="15"/>
       <c r="F108" s="26"/>
       <c r="G108" s="26"/>
@@ -8641,15 +8633,15 @@
       <c r="Y108" s="27"/>
       <c r="Z108" s="27"/>
       <c r="AA108" s="27"/>
-      <c r="AB108" s="76"/>
-      <c r="AC108" s="77"/>
-      <c r="AD108" s="77"/>
-      <c r="AE108" s="77"/>
-      <c r="AF108" s="77"/>
-      <c r="AG108" s="77"/>
-      <c r="AH108" s="78"/>
-    </row>
-    <row r="109" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB108" s="54"/>
+      <c r="AC108" s="55"/>
+      <c r="AD108" s="55"/>
+      <c r="AE108" s="55"/>
+      <c r="AF108" s="55"/>
+      <c r="AG108" s="55"/>
+      <c r="AH108" s="56"/>
+    </row>
+    <row r="109" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E109" s="15"/>
       <c r="F109" s="26"/>
       <c r="G109" s="26"/>
@@ -8673,15 +8665,15 @@
       <c r="Y109" s="27"/>
       <c r="Z109" s="27"/>
       <c r="AA109" s="27"/>
-      <c r="AB109" s="76"/>
-      <c r="AC109" s="77"/>
-      <c r="AD109" s="77"/>
-      <c r="AE109" s="77"/>
-      <c r="AF109" s="77"/>
-      <c r="AG109" s="77"/>
-      <c r="AH109" s="78"/>
-    </row>
-    <row r="110" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB109" s="54"/>
+      <c r="AC109" s="55"/>
+      <c r="AD109" s="55"/>
+      <c r="AE109" s="55"/>
+      <c r="AF109" s="55"/>
+      <c r="AG109" s="55"/>
+      <c r="AH109" s="56"/>
+    </row>
+    <row r="110" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E110" s="15"/>
       <c r="F110" s="26"/>
       <c r="G110" s="26"/>
@@ -8705,15 +8697,15 @@
       <c r="Y110" s="27"/>
       <c r="Z110" s="27"/>
       <c r="AA110" s="27"/>
-      <c r="AB110" s="76"/>
-      <c r="AC110" s="77"/>
-      <c r="AD110" s="77"/>
-      <c r="AE110" s="77"/>
-      <c r="AF110" s="77"/>
-      <c r="AG110" s="77"/>
-      <c r="AH110" s="78"/>
-    </row>
-    <row r="111" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB110" s="54"/>
+      <c r="AC110" s="55"/>
+      <c r="AD110" s="55"/>
+      <c r="AE110" s="55"/>
+      <c r="AF110" s="55"/>
+      <c r="AG110" s="55"/>
+      <c r="AH110" s="56"/>
+    </row>
+    <row r="111" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E111" s="15"/>
       <c r="F111" s="29"/>
       <c r="G111" s="29"/>
@@ -8737,49 +8729,49 @@
       <c r="Y111" s="30"/>
       <c r="Z111" s="30"/>
       <c r="AA111" s="30"/>
-      <c r="AB111" s="79"/>
-      <c r="AC111" s="80"/>
-      <c r="AD111" s="80"/>
-      <c r="AE111" s="80"/>
-      <c r="AF111" s="80"/>
-      <c r="AG111" s="80"/>
-      <c r="AH111" s="81"/>
-    </row>
-    <row r="112" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB111" s="57"/>
+      <c r="AC111" s="58"/>
+      <c r="AD111" s="58"/>
+      <c r="AE111" s="58"/>
+      <c r="AF111" s="58"/>
+      <c r="AG111" s="58"/>
+      <c r="AH111" s="59"/>
+    </row>
+    <row r="112" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E112" s="15"/>
-      <c r="F112" s="90" t="s">
+      <c r="F112" s="71" t="s">
         <v>54</v>
       </c>
-      <c r="G112" s="91"/>
-      <c r="H112" s="91"/>
-      <c r="I112" s="91"/>
-      <c r="J112" s="91"/>
-      <c r="K112" s="91"/>
-      <c r="L112" s="91"/>
-      <c r="M112" s="91"/>
-      <c r="N112" s="91"/>
-      <c r="O112" s="91"/>
-      <c r="P112" s="91"/>
-      <c r="Q112" s="91"/>
-      <c r="R112" s="91"/>
-      <c r="S112" s="91"/>
-      <c r="T112" s="91"/>
-      <c r="U112" s="91"/>
-      <c r="V112" s="91"/>
-      <c r="W112" s="91"/>
-      <c r="X112" s="91"/>
-      <c r="Y112" s="91"/>
-      <c r="Z112" s="91"/>
-      <c r="AA112" s="91"/>
-      <c r="AB112" s="91"/>
-      <c r="AC112" s="91"/>
-      <c r="AD112" s="91"/>
-      <c r="AE112" s="91"/>
-      <c r="AF112" s="91"/>
-      <c r="AG112" s="91"/>
-      <c r="AH112" s="92"/>
-    </row>
-    <row r="113" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="G112" s="72"/>
+      <c r="H112" s="72"/>
+      <c r="I112" s="72"/>
+      <c r="J112" s="72"/>
+      <c r="K112" s="72"/>
+      <c r="L112" s="72"/>
+      <c r="M112" s="72"/>
+      <c r="N112" s="72"/>
+      <c r="O112" s="72"/>
+      <c r="P112" s="72"/>
+      <c r="Q112" s="72"/>
+      <c r="R112" s="72"/>
+      <c r="S112" s="72"/>
+      <c r="T112" s="72"/>
+      <c r="U112" s="72"/>
+      <c r="V112" s="72"/>
+      <c r="W112" s="72"/>
+      <c r="X112" s="72"/>
+      <c r="Y112" s="72"/>
+      <c r="Z112" s="72"/>
+      <c r="AA112" s="72"/>
+      <c r="AB112" s="72"/>
+      <c r="AC112" s="72"/>
+      <c r="AD112" s="72"/>
+      <c r="AE112" s="72"/>
+      <c r="AF112" s="72"/>
+      <c r="AG112" s="72"/>
+      <c r="AH112" s="73"/>
+    </row>
+    <row r="113" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E113" s="15"/>
       <c r="F113" s="23">
         <v>8</v>
@@ -8805,17 +8797,17 @@
       <c r="Y113" s="24"/>
       <c r="Z113" s="24"/>
       <c r="AA113" s="25"/>
-      <c r="AB113" s="73" t="s">
+      <c r="AB113" s="51" t="s">
         <v>65</v>
       </c>
-      <c r="AC113" s="74"/>
-      <c r="AD113" s="74"/>
-      <c r="AE113" s="74"/>
-      <c r="AF113" s="74"/>
-      <c r="AG113" s="74"/>
-      <c r="AH113" s="75"/>
-    </row>
-    <row r="114" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC113" s="52"/>
+      <c r="AD113" s="52"/>
+      <c r="AE113" s="52"/>
+      <c r="AF113" s="52"/>
+      <c r="AG113" s="52"/>
+      <c r="AH113" s="53"/>
+    </row>
+    <row r="114" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E114" s="15"/>
       <c r="F114" s="26"/>
       <c r="G114" s="26"/>
@@ -8839,15 +8831,15 @@
       <c r="Y114" s="27"/>
       <c r="Z114" s="27"/>
       <c r="AA114" s="28"/>
-      <c r="AB114" s="76"/>
-      <c r="AC114" s="77"/>
-      <c r="AD114" s="77"/>
-      <c r="AE114" s="77"/>
-      <c r="AF114" s="77"/>
-      <c r="AG114" s="77"/>
-      <c r="AH114" s="78"/>
-    </row>
-    <row r="115" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB114" s="54"/>
+      <c r="AC114" s="55"/>
+      <c r="AD114" s="55"/>
+      <c r="AE114" s="55"/>
+      <c r="AF114" s="55"/>
+      <c r="AG114" s="55"/>
+      <c r="AH114" s="56"/>
+    </row>
+    <row r="115" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E115" s="15"/>
       <c r="F115" s="26"/>
       <c r="G115" s="26"/>
@@ -8871,15 +8863,15 @@
       <c r="Y115" s="27"/>
       <c r="Z115" s="27"/>
       <c r="AA115" s="28"/>
-      <c r="AB115" s="76"/>
-      <c r="AC115" s="77"/>
-      <c r="AD115" s="77"/>
-      <c r="AE115" s="77"/>
-      <c r="AF115" s="77"/>
-      <c r="AG115" s="77"/>
-      <c r="AH115" s="78"/>
-    </row>
-    <row r="116" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB115" s="54"/>
+      <c r="AC115" s="55"/>
+      <c r="AD115" s="55"/>
+      <c r="AE115" s="55"/>
+      <c r="AF115" s="55"/>
+      <c r="AG115" s="55"/>
+      <c r="AH115" s="56"/>
+    </row>
+    <row r="116" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E116" s="15"/>
       <c r="F116" s="26"/>
       <c r="G116" s="26"/>
@@ -8903,15 +8895,15 @@
       <c r="Y116" s="27"/>
       <c r="Z116" s="27"/>
       <c r="AA116" s="27"/>
-      <c r="AB116" s="76"/>
-      <c r="AC116" s="77"/>
-      <c r="AD116" s="77"/>
-      <c r="AE116" s="77"/>
-      <c r="AF116" s="77"/>
-      <c r="AG116" s="77"/>
-      <c r="AH116" s="78"/>
-    </row>
-    <row r="117" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB116" s="54"/>
+      <c r="AC116" s="55"/>
+      <c r="AD116" s="55"/>
+      <c r="AE116" s="55"/>
+      <c r="AF116" s="55"/>
+      <c r="AG116" s="55"/>
+      <c r="AH116" s="56"/>
+    </row>
+    <row r="117" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E117" s="15"/>
       <c r="F117" s="26"/>
       <c r="G117" s="26"/>
@@ -8935,15 +8927,15 @@
       <c r="Y117" s="27"/>
       <c r="Z117" s="27"/>
       <c r="AA117" s="27"/>
-      <c r="AB117" s="76"/>
-      <c r="AC117" s="77"/>
-      <c r="AD117" s="77"/>
-      <c r="AE117" s="77"/>
-      <c r="AF117" s="77"/>
-      <c r="AG117" s="77"/>
-      <c r="AH117" s="78"/>
-    </row>
-    <row r="118" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB117" s="54"/>
+      <c r="AC117" s="55"/>
+      <c r="AD117" s="55"/>
+      <c r="AE117" s="55"/>
+      <c r="AF117" s="55"/>
+      <c r="AG117" s="55"/>
+      <c r="AH117" s="56"/>
+    </row>
+    <row r="118" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E118" s="15"/>
       <c r="F118" s="26"/>
       <c r="G118" s="26"/>
@@ -8967,15 +8959,15 @@
       <c r="Y118" s="27"/>
       <c r="Z118" s="27"/>
       <c r="AA118" s="27"/>
-      <c r="AB118" s="76"/>
-      <c r="AC118" s="77"/>
-      <c r="AD118" s="77"/>
-      <c r="AE118" s="77"/>
-      <c r="AF118" s="77"/>
-      <c r="AG118" s="77"/>
-      <c r="AH118" s="78"/>
-    </row>
-    <row r="119" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB118" s="54"/>
+      <c r="AC118" s="55"/>
+      <c r="AD118" s="55"/>
+      <c r="AE118" s="55"/>
+      <c r="AF118" s="55"/>
+      <c r="AG118" s="55"/>
+      <c r="AH118" s="56"/>
+    </row>
+    <row r="119" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E119" s="15"/>
       <c r="F119" s="26"/>
       <c r="G119" s="26"/>
@@ -8999,15 +8991,15 @@
       <c r="Y119" s="27"/>
       <c r="Z119" s="27"/>
       <c r="AA119" s="27"/>
-      <c r="AB119" s="76"/>
-      <c r="AC119" s="77"/>
-      <c r="AD119" s="77"/>
-      <c r="AE119" s="77"/>
-      <c r="AF119" s="77"/>
-      <c r="AG119" s="77"/>
-      <c r="AH119" s="78"/>
-    </row>
-    <row r="120" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB119" s="54"/>
+      <c r="AC119" s="55"/>
+      <c r="AD119" s="55"/>
+      <c r="AE119" s="55"/>
+      <c r="AF119" s="55"/>
+      <c r="AG119" s="55"/>
+      <c r="AH119" s="56"/>
+    </row>
+    <row r="120" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E120" s="15"/>
       <c r="F120" s="26"/>
       <c r="G120" s="26"/>
@@ -9031,15 +9023,15 @@
       <c r="Y120" s="27"/>
       <c r="Z120" s="27"/>
       <c r="AA120" s="27"/>
-      <c r="AB120" s="76"/>
-      <c r="AC120" s="77"/>
-      <c r="AD120" s="77"/>
-      <c r="AE120" s="77"/>
-      <c r="AF120" s="77"/>
-      <c r="AG120" s="77"/>
-      <c r="AH120" s="78"/>
-    </row>
-    <row r="121" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB120" s="54"/>
+      <c r="AC120" s="55"/>
+      <c r="AD120" s="55"/>
+      <c r="AE120" s="55"/>
+      <c r="AF120" s="55"/>
+      <c r="AG120" s="55"/>
+      <c r="AH120" s="56"/>
+    </row>
+    <row r="121" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E121" s="15"/>
       <c r="F121" s="26"/>
       <c r="G121" s="26"/>
@@ -9063,15 +9055,15 @@
       <c r="Y121" s="27"/>
       <c r="Z121" s="27"/>
       <c r="AA121" s="27"/>
-      <c r="AB121" s="76"/>
-      <c r="AC121" s="77"/>
-      <c r="AD121" s="77"/>
-      <c r="AE121" s="77"/>
-      <c r="AF121" s="77"/>
-      <c r="AG121" s="77"/>
-      <c r="AH121" s="78"/>
-    </row>
-    <row r="122" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB121" s="54"/>
+      <c r="AC121" s="55"/>
+      <c r="AD121" s="55"/>
+      <c r="AE121" s="55"/>
+      <c r="AF121" s="55"/>
+      <c r="AG121" s="55"/>
+      <c r="AH121" s="56"/>
+    </row>
+    <row r="122" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E122" s="15"/>
       <c r="F122" s="26"/>
       <c r="G122" s="26"/>
@@ -9095,15 +9087,15 @@
       <c r="Y122" s="27"/>
       <c r="Z122" s="27"/>
       <c r="AA122" s="27"/>
-      <c r="AB122" s="76"/>
-      <c r="AC122" s="77"/>
-      <c r="AD122" s="77"/>
-      <c r="AE122" s="77"/>
-      <c r="AF122" s="77"/>
-      <c r="AG122" s="77"/>
-      <c r="AH122" s="78"/>
-    </row>
-    <row r="123" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB122" s="54"/>
+      <c r="AC122" s="55"/>
+      <c r="AD122" s="55"/>
+      <c r="AE122" s="55"/>
+      <c r="AF122" s="55"/>
+      <c r="AG122" s="55"/>
+      <c r="AH122" s="56"/>
+    </row>
+    <row r="123" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E123" s="15"/>
       <c r="F123" s="29"/>
       <c r="G123" s="29"/>
@@ -9127,15 +9119,15 @@
       <c r="Y123" s="30"/>
       <c r="Z123" s="30"/>
       <c r="AA123" s="30"/>
-      <c r="AB123" s="79"/>
-      <c r="AC123" s="80"/>
-      <c r="AD123" s="80"/>
-      <c r="AE123" s="80"/>
-      <c r="AF123" s="80"/>
-      <c r="AG123" s="80"/>
-      <c r="AH123" s="81"/>
-    </row>
-    <row r="124" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB123" s="57"/>
+      <c r="AC123" s="58"/>
+      <c r="AD123" s="58"/>
+      <c r="AE123" s="58"/>
+      <c r="AF123" s="58"/>
+      <c r="AG123" s="58"/>
+      <c r="AH123" s="59"/>
+    </row>
+    <row r="124" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E124" s="15"/>
       <c r="F124" s="23">
         <v>9</v>
@@ -9161,17 +9153,17 @@
       <c r="Y124" s="24"/>
       <c r="Z124" s="24"/>
       <c r="AA124" s="25"/>
-      <c r="AB124" s="73" t="s">
+      <c r="AB124" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="AC124" s="74"/>
-      <c r="AD124" s="74"/>
-      <c r="AE124" s="74"/>
-      <c r="AF124" s="74"/>
-      <c r="AG124" s="74"/>
-      <c r="AH124" s="75"/>
-    </row>
-    <row r="125" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AC124" s="52"/>
+      <c r="AD124" s="52"/>
+      <c r="AE124" s="52"/>
+      <c r="AF124" s="52"/>
+      <c r="AG124" s="52"/>
+      <c r="AH124" s="53"/>
+    </row>
+    <row r="125" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E125" s="15"/>
       <c r="F125" s="26"/>
       <c r="G125" s="26"/>
@@ -9195,15 +9187,15 @@
       <c r="Y125" s="27"/>
       <c r="Z125" s="27"/>
       <c r="AA125" s="28"/>
-      <c r="AB125" s="76"/>
-      <c r="AC125" s="77"/>
-      <c r="AD125" s="77"/>
-      <c r="AE125" s="77"/>
-      <c r="AF125" s="77"/>
-      <c r="AG125" s="77"/>
-      <c r="AH125" s="78"/>
-    </row>
-    <row r="126" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB125" s="54"/>
+      <c r="AC125" s="55"/>
+      <c r="AD125" s="55"/>
+      <c r="AE125" s="55"/>
+      <c r="AF125" s="55"/>
+      <c r="AG125" s="55"/>
+      <c r="AH125" s="56"/>
+    </row>
+    <row r="126" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E126" s="15"/>
       <c r="F126" s="26"/>
       <c r="G126" s="26"/>
@@ -9227,15 +9219,15 @@
       <c r="Y126" s="27"/>
       <c r="Z126" s="27"/>
       <c r="AA126" s="27"/>
-      <c r="AB126" s="76"/>
-      <c r="AC126" s="77"/>
-      <c r="AD126" s="77"/>
-      <c r="AE126" s="77"/>
-      <c r="AF126" s="77"/>
-      <c r="AG126" s="77"/>
-      <c r="AH126" s="78"/>
-    </row>
-    <row r="127" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB126" s="54"/>
+      <c r="AC126" s="55"/>
+      <c r="AD126" s="55"/>
+      <c r="AE126" s="55"/>
+      <c r="AF126" s="55"/>
+      <c r="AG126" s="55"/>
+      <c r="AH126" s="56"/>
+    </row>
+    <row r="127" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E127" s="15"/>
       <c r="F127" s="26"/>
       <c r="G127" s="26"/>
@@ -9259,15 +9251,15 @@
       <c r="Y127" s="27"/>
       <c r="Z127" s="27"/>
       <c r="AA127" s="27"/>
-      <c r="AB127" s="76"/>
-      <c r="AC127" s="77"/>
-      <c r="AD127" s="77"/>
-      <c r="AE127" s="77"/>
-      <c r="AF127" s="77"/>
-      <c r="AG127" s="77"/>
-      <c r="AH127" s="78"/>
-    </row>
-    <row r="128" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB127" s="54"/>
+      <c r="AC127" s="55"/>
+      <c r="AD127" s="55"/>
+      <c r="AE127" s="55"/>
+      <c r="AF127" s="55"/>
+      <c r="AG127" s="55"/>
+      <c r="AH127" s="56"/>
+    </row>
+    <row r="128" spans="5:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E128" s="15"/>
       <c r="F128" s="26"/>
       <c r="G128" s="26"/>
@@ -9291,15 +9283,15 @@
       <c r="Y128" s="27"/>
       <c r="Z128" s="27"/>
       <c r="AA128" s="27"/>
-      <c r="AB128" s="76"/>
-      <c r="AC128" s="77"/>
-      <c r="AD128" s="77"/>
-      <c r="AE128" s="77"/>
-      <c r="AF128" s="77"/>
-      <c r="AG128" s="77"/>
-      <c r="AH128" s="78"/>
-    </row>
-    <row r="129" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB128" s="54"/>
+      <c r="AC128" s="55"/>
+      <c r="AD128" s="55"/>
+      <c r="AE128" s="55"/>
+      <c r="AF128" s="55"/>
+      <c r="AG128" s="55"/>
+      <c r="AH128" s="56"/>
+    </row>
+    <row r="129" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E129" s="15"/>
       <c r="F129" s="26"/>
       <c r="G129" s="26"/>
@@ -9323,15 +9315,15 @@
       <c r="Y129" s="27"/>
       <c r="Z129" s="27"/>
       <c r="AA129" s="27"/>
-      <c r="AB129" s="76"/>
-      <c r="AC129" s="77"/>
-      <c r="AD129" s="77"/>
-      <c r="AE129" s="77"/>
-      <c r="AF129" s="77"/>
-      <c r="AG129" s="77"/>
-      <c r="AH129" s="78"/>
-    </row>
-    <row r="130" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB129" s="54"/>
+      <c r="AC129" s="55"/>
+      <c r="AD129" s="55"/>
+      <c r="AE129" s="55"/>
+      <c r="AF129" s="55"/>
+      <c r="AG129" s="55"/>
+      <c r="AH129" s="56"/>
+    </row>
+    <row r="130" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E130" s="15"/>
       <c r="F130" s="26"/>
       <c r="G130" s="26"/>
@@ -9355,15 +9347,15 @@
       <c r="Y130" s="27"/>
       <c r="Z130" s="27"/>
       <c r="AA130" s="27"/>
-      <c r="AB130" s="76"/>
-      <c r="AC130" s="77"/>
-      <c r="AD130" s="77"/>
-      <c r="AE130" s="77"/>
-      <c r="AF130" s="77"/>
-      <c r="AG130" s="77"/>
-      <c r="AH130" s="78"/>
-    </row>
-    <row r="131" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB130" s="54"/>
+      <c r="AC130" s="55"/>
+      <c r="AD130" s="55"/>
+      <c r="AE130" s="55"/>
+      <c r="AF130" s="55"/>
+      <c r="AG130" s="55"/>
+      <c r="AH130" s="56"/>
+    </row>
+    <row r="131" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E131" s="15"/>
       <c r="F131" s="26"/>
       <c r="G131" s="26"/>
@@ -9387,15 +9379,15 @@
       <c r="Y131" s="27"/>
       <c r="Z131" s="27"/>
       <c r="AA131" s="27"/>
-      <c r="AB131" s="76"/>
-      <c r="AC131" s="77"/>
-      <c r="AD131" s="77"/>
-      <c r="AE131" s="77"/>
-      <c r="AF131" s="77"/>
-      <c r="AG131" s="77"/>
-      <c r="AH131" s="78"/>
-    </row>
-    <row r="132" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB131" s="54"/>
+      <c r="AC131" s="55"/>
+      <c r="AD131" s="55"/>
+      <c r="AE131" s="55"/>
+      <c r="AF131" s="55"/>
+      <c r="AG131" s="55"/>
+      <c r="AH131" s="56"/>
+    </row>
+    <row r="132" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E132" s="15"/>
       <c r="F132" s="29"/>
       <c r="G132" s="29"/>
@@ -9419,18 +9411,18 @@
       <c r="Y132" s="30"/>
       <c r="Z132" s="30"/>
       <c r="AA132" s="30"/>
-      <c r="AB132" s="79"/>
-      <c r="AC132" s="80"/>
-      <c r="AD132" s="80"/>
-      <c r="AE132" s="80"/>
-      <c r="AF132" s="80"/>
-      <c r="AG132" s="80"/>
-      <c r="AH132" s="81"/>
-    </row>
-    <row r="133" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB132" s="57"/>
+      <c r="AC132" s="58"/>
+      <c r="AD132" s="58"/>
+      <c r="AE132" s="58"/>
+      <c r="AF132" s="58"/>
+      <c r="AG132" s="58"/>
+      <c r="AH132" s="59"/>
+    </row>
+    <row r="133" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E133" s="15"/>
     </row>
-    <row r="134" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E134" s="15"/>
       <c r="F134" s="4" t="s">
         <v>48</v>
@@ -9439,29 +9431,29 @@
         <v>51</v>
       </c>
     </row>
-    <row r="135" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E135" s="15"/>
       <c r="H135" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="136" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="4:34" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E136" s="15"/>
       <c r="H136" s="4" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="137" spans="4:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="4:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D137" s="18"/>
       <c r="H137" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="138" spans="4:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="4:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D138" s="18"/>
     </row>
-    <row r="139" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="140" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="139" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="140" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D140" s="15" t="str">
         <f>$C$7&amp;"3."</f>
         <v>6.2.3.</v>
@@ -9470,14 +9462,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="141" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="141" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="E141" s="16" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="142" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="143" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="144" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="142" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="143" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="144" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D144" s="15" t="str">
         <f>$C$7&amp;"4."</f>
         <v>6.2.4.</v>
@@ -9486,7 +9478,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="145" spans="4:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="4:34" s="16" customFormat="1" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E145" s="16" t="s">
         <v>57</v>
       </c>
@@ -9520,11 +9512,11 @@
       <c r="AG145" s="17"/>
       <c r="AH145" s="17"/>
     </row>
-    <row r="146" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="146" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D146" s="15"/>
     </row>
-    <row r="147" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="148" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="147" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="148" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D148" s="15" t="str">
         <f>$C$7&amp;"5."</f>
         <v>6.2.5.</v>
@@ -9533,18 +9525,18 @@
         <v>16</v>
       </c>
     </row>
-    <row r="149" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="149" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="E149" s="16" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="150" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="150" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="E150" s="16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="151" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="152" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="151" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="152" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="E152" s="18" t="s">
         <v>25</v>
       </c>
@@ -9552,18 +9544,18 @@
         <v>26</v>
       </c>
     </row>
-    <row r="153" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="153" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="F153" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="154" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="154" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="F154" s="16" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="155" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="156" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="155" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="156" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="D156" s="15" t="str">
         <f>$C$7&amp;"6."</f>
         <v>6.2.6.</v>
@@ -9572,13 +9564,13 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="157" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="E157" s="16" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="158" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="159" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="158" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="159" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="E159" s="18" t="s">
         <v>25</v>
       </c>
@@ -9586,454 +9578,464 @@
         <v>66</v>
       </c>
     </row>
-    <row r="160" spans="4:34" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="160" spans="4:34" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="F160" s="16" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="161" spans="4:6" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2">
+    <row r="161" spans="4:6" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15">
       <c r="F161" s="16" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="162" spans="4:6" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="163" spans="4:6" s="16" customFormat="1" ht="11" x14ac:dyDescent="0.2"/>
-    <row r="164" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="4:6" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="163" spans="4:6" s="16" customFormat="1" ht="11.25" x14ac:dyDescent="0.15"/>
+    <row r="164" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="D164" s="16"/>
     </row>
-    <row r="165" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="11.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="165" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" spans="4:6" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="11.25" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="E1:O1"/>
+    <mergeCell ref="R1:X1"/>
+    <mergeCell ref="AA1:AE1"/>
+    <mergeCell ref="AF1:AI1"/>
+    <mergeCell ref="E2:O2"/>
+    <mergeCell ref="R2:X3"/>
+    <mergeCell ref="AA2:AE2"/>
+    <mergeCell ref="AF2:AI2"/>
+    <mergeCell ref="E3:O3"/>
+    <mergeCell ref="AA3:AE3"/>
     <mergeCell ref="AB124:AH132"/>
     <mergeCell ref="AB91:AH102"/>
     <mergeCell ref="AB103:AH111"/>
@@ -10045,16 +10047,6 @@
     <mergeCell ref="AB43:AH54"/>
     <mergeCell ref="AB34:AH42"/>
     <mergeCell ref="F112:AH112"/>
-    <mergeCell ref="E1:O1"/>
-    <mergeCell ref="R1:X1"/>
-    <mergeCell ref="AA1:AE1"/>
-    <mergeCell ref="AF1:AI1"/>
-    <mergeCell ref="E2:O2"/>
-    <mergeCell ref="R2:X3"/>
-    <mergeCell ref="AA2:AE2"/>
-    <mergeCell ref="AF2:AI2"/>
-    <mergeCell ref="E3:O3"/>
-    <mergeCell ref="AA3:AE3"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
